--- a/DA PORTAL.xlsx
+++ b/DA PORTAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\downlodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E90289-1E4F-4B68-8308-D3ADEF632FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBFC902-4386-48C9-9887-E89DF0882445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15510" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONAL INFORMATION" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9165" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9165" uniqueCount="1361">
   <si>
     <t>Name</t>
   </si>
@@ -4142,6 +4142,9 @@
   </si>
   <si>
     <t>PONDICHERRY UNIVERSITY</t>
+  </si>
+  <si>
+    <t>Intern Project</t>
   </si>
 </sst>
 </file>
@@ -4844,7 +4847,7 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -46629,7 +46632,7 @@
       <c r="B438" s="108" t="s">
         <v>1262</v>
       </c>
-      <c r="C438" s="108" t="s">
+      <c r="C438" s="116" t="s">
         <v>1251</v>
       </c>
       <c r="D438" s="108">
@@ -46661,7 +46664,7 @@
       <c r="B439" s="111" t="s">
         <v>1268</v>
       </c>
-      <c r="C439" s="111" t="s">
+      <c r="C439" s="117" t="s">
         <v>1256</v>
       </c>
       <c r="D439" s="111">
@@ -46693,7 +46696,7 @@
       <c r="B440" s="114" t="s">
         <v>1270</v>
       </c>
-      <c r="C440" s="114" t="s">
+      <c r="C440" s="118" t="s">
         <v>1258</v>
       </c>
       <c r="D440" s="114">
@@ -46725,7 +46728,7 @@
       <c r="B441" s="111" t="s">
         <v>1272</v>
       </c>
-      <c r="C441" s="111" t="s">
+      <c r="C441" s="117" t="s">
         <v>1260</v>
       </c>
       <c r="D441" s="111">
@@ -46757,8 +46760,8 @@
       <c r="B442" s="114" t="s">
         <v>1275</v>
       </c>
-      <c r="C442" s="114" t="s">
-        <v>1230</v>
+      <c r="C442" s="118" t="s">
+        <v>1259</v>
       </c>
       <c r="D442" s="114">
         <v>7.5</v>
@@ -46789,7 +46792,7 @@
       <c r="B443" s="111" t="s">
         <v>1278</v>
       </c>
-      <c r="C443" s="111" t="s">
+      <c r="C443" s="117" t="s">
         <v>1255</v>
       </c>
       <c r="D443" s="111">
@@ -46821,8 +46824,8 @@
       <c r="B444" s="114" t="s">
         <v>1281</v>
       </c>
-      <c r="C444" s="114" t="s">
-        <v>1259</v>
+      <c r="C444" s="118" t="s">
+        <v>1250</v>
       </c>
       <c r="D444" s="114">
         <v>8</v>
@@ -46853,8 +46856,8 @@
       <c r="B445" s="111" t="s">
         <v>1284</v>
       </c>
-      <c r="C445" s="111" t="s">
-        <v>1250</v>
+      <c r="C445" s="119" t="s">
+        <v>1257</v>
       </c>
       <c r="D445" s="111">
         <v>7</v>
@@ -46885,8 +46888,8 @@
       <c r="B446" s="114" t="s">
         <v>1286</v>
       </c>
-      <c r="C446" s="119" t="s">
-        <v>1257</v>
+      <c r="C446" s="118" t="s">
+        <v>1254</v>
       </c>
       <c r="D446" s="114">
         <v>8</v>
@@ -46917,8 +46920,8 @@
       <c r="B447" s="111" t="s">
         <v>1289</v>
       </c>
-      <c r="C447" s="111" t="s">
-        <v>1254</v>
+      <c r="C447" s="117" t="s">
+        <v>1251</v>
       </c>
       <c r="D447" s="111">
         <v>7</v>
@@ -46949,8 +46952,8 @@
       <c r="B448" s="114" t="s">
         <v>1292</v>
       </c>
-      <c r="C448" s="114" t="s">
-        <v>1251</v>
+      <c r="C448" s="118" t="s">
+        <v>1256</v>
       </c>
       <c r="D448" s="114">
         <v>6</v>
@@ -46981,8 +46984,8 @@
       <c r="B449" s="111" t="s">
         <v>1296</v>
       </c>
-      <c r="C449" s="111" t="s">
-        <v>1256</v>
+      <c r="C449" s="117" t="s">
+        <v>1230</v>
       </c>
       <c r="D449" s="111">
         <v>8</v>
@@ -47013,7 +47016,7 @@
       <c r="B450" s="114" t="s">
         <v>1299</v>
       </c>
-      <c r="C450" s="114" t="s">
+      <c r="C450" s="118" t="s">
         <v>1258</v>
       </c>
       <c r="D450" s="114">
@@ -47045,8 +47048,8 @@
       <c r="B451" s="111" t="s">
         <v>1301</v>
       </c>
-      <c r="C451" s="111" t="s">
-        <v>1260</v>
+      <c r="C451" s="117" t="s">
+        <v>1255</v>
       </c>
       <c r="D451" s="111">
         <v>8</v>
@@ -47077,8 +47080,8 @@
       <c r="B452" s="114" t="s">
         <v>1304</v>
       </c>
-      <c r="C452" s="114" t="s">
-        <v>1230</v>
+      <c r="C452" s="118" t="s">
+        <v>1259</v>
       </c>
       <c r="D452" s="114">
         <v>7</v>
@@ -47109,8 +47112,8 @@
       <c r="B453" s="111" t="s">
         <v>1307</v>
       </c>
-      <c r="C453" s="111" t="s">
-        <v>1255</v>
+      <c r="C453" s="117" t="s">
+        <v>1250</v>
       </c>
       <c r="D453" s="111">
         <v>7</v>
@@ -47141,8 +47144,8 @@
       <c r="B454" s="114" t="s">
         <v>1309</v>
       </c>
-      <c r="C454" s="114" t="s">
-        <v>1259</v>
+      <c r="C454" s="118" t="s">
+        <v>1254</v>
       </c>
       <c r="D454" s="114">
         <v>7</v>
@@ -47173,8 +47176,8 @@
       <c r="B455" s="111" t="s">
         <v>1311</v>
       </c>
-      <c r="C455" s="111" t="s">
-        <v>1250</v>
+      <c r="C455" s="117" t="s">
+        <v>1252</v>
       </c>
       <c r="D455" s="111">
         <v>7</v>
@@ -47205,8 +47208,8 @@
       <c r="B456" s="114" t="s">
         <v>1313</v>
       </c>
-      <c r="C456" s="114" t="s">
-        <v>1257</v>
+      <c r="C456" s="118" t="s">
+        <v>1251</v>
       </c>
       <c r="D456" s="114">
         <v>6</v>
@@ -47237,8 +47240,8 @@
       <c r="B457" s="111" t="s">
         <v>1315</v>
       </c>
-      <c r="C457" s="111" t="s">
-        <v>1254</v>
+      <c r="C457" s="117" t="s">
+        <v>1256</v>
       </c>
       <c r="D457" s="111">
         <v>7</v>
@@ -47269,8 +47272,8 @@
       <c r="B458" s="114" t="s">
         <v>1317</v>
       </c>
-      <c r="C458" s="114" t="s">
-        <v>1251</v>
+      <c r="C458" s="118" t="s">
+        <v>1258</v>
       </c>
       <c r="D458" s="114">
         <v>7</v>
@@ -47301,8 +47304,8 @@
       <c r="B459" s="111" t="s">
         <v>1320</v>
       </c>
-      <c r="C459" s="111" t="s">
-        <v>1256</v>
+      <c r="C459" s="117" t="s">
+        <v>1250</v>
       </c>
       <c r="D459" s="111">
         <v>6</v>
@@ -47333,8 +47336,8 @@
       <c r="B460" s="114" t="s">
         <v>1322</v>
       </c>
-      <c r="C460" s="114" t="s">
-        <v>1258</v>
+      <c r="C460" s="118" t="s">
+        <v>1257</v>
       </c>
       <c r="D460" s="114">
         <v>6</v>
@@ -47365,8 +47368,8 @@
       <c r="B461" s="111" t="s">
         <v>1324</v>
       </c>
-      <c r="C461" s="111" t="s">
-        <v>1260</v>
+      <c r="C461" s="117" t="s">
+        <v>1254</v>
       </c>
       <c r="D461" s="111">
         <v>7</v>
@@ -47397,8 +47400,8 @@
       <c r="B462" s="114" t="s">
         <v>1327</v>
       </c>
-      <c r="C462" s="114" t="s">
-        <v>1230</v>
+      <c r="C462" s="118" t="s">
+        <v>1252</v>
       </c>
       <c r="D462" s="114">
         <v>7</v>
@@ -47429,8 +47432,8 @@
       <c r="B463" s="111" t="s">
         <v>1329</v>
       </c>
-      <c r="C463" s="111" t="s">
-        <v>1255</v>
+      <c r="C463" s="117" t="s">
+        <v>1251</v>
       </c>
       <c r="D463" s="111">
         <v>8</v>
@@ -47461,8 +47464,8 @@
       <c r="B464" s="114" t="s">
         <v>1331</v>
       </c>
-      <c r="C464" s="114" t="s">
-        <v>1259</v>
+      <c r="C464" s="118" t="s">
+        <v>1258</v>
       </c>
       <c r="D464" s="114">
         <v>8</v>
@@ -47493,8 +47496,8 @@
       <c r="B465" s="111" t="s">
         <v>1334</v>
       </c>
-      <c r="C465" s="111" t="s">
-        <v>1250</v>
+      <c r="C465" s="117" t="s">
+        <v>1360</v>
       </c>
       <c r="D465" s="111">
         <v>7</v>
@@ -47525,8 +47528,8 @@
       <c r="B466" s="114" t="s">
         <v>1337</v>
       </c>
-      <c r="C466" s="114" t="s">
-        <v>1257</v>
+      <c r="C466" s="118" t="s">
+        <v>1260</v>
       </c>
       <c r="D466" s="114">
         <v>8</v>
@@ -47557,8 +47560,8 @@
       <c r="B467" s="111" t="s">
         <v>1340</v>
       </c>
-      <c r="C467" s="111" t="s">
-        <v>1254</v>
+      <c r="C467" s="117" t="s">
+        <v>1230</v>
       </c>
       <c r="D467" s="111">
         <v>7</v>
@@ -47589,8 +47592,8 @@
       <c r="B468" s="114" t="s">
         <v>1342</v>
       </c>
-      <c r="C468" s="114" t="s">
-        <v>1256</v>
+      <c r="C468" s="118" t="s">
+        <v>1255</v>
       </c>
       <c r="D468" s="114">
         <v>8</v>
@@ -47621,8 +47624,8 @@
       <c r="B469" s="111" t="s">
         <v>1344</v>
       </c>
-      <c r="C469" s="111" t="s">
-        <v>1258</v>
+      <c r="C469" s="117" t="s">
+        <v>1259</v>
       </c>
       <c r="D469" s="111">
         <v>8</v>
@@ -47653,8 +47656,8 @@
       <c r="B470" s="114" t="s">
         <v>1347</v>
       </c>
-      <c r="C470" s="114" t="s">
-        <v>1260</v>
+      <c r="C470" s="118" t="s">
+        <v>1257</v>
       </c>
       <c r="D470" s="114">
         <v>7</v>
@@ -47685,8 +47688,8 @@
       <c r="B471" s="111" t="s">
         <v>1349</v>
       </c>
-      <c r="C471" s="111" t="s">
-        <v>1230</v>
+      <c r="C471" s="117" t="s">
+        <v>1252</v>
       </c>
       <c r="D471" s="111">
         <v>8</v>
@@ -47717,8 +47720,8 @@
       <c r="B472" s="114" t="s">
         <v>1351</v>
       </c>
-      <c r="C472" s="114" t="s">
-        <v>1255</v>
+      <c r="C472" s="118" t="s">
+        <v>1251</v>
       </c>
       <c r="D472" s="114">
         <v>8</v>
@@ -47749,8 +47752,8 @@
       <c r="B473" s="111" t="s">
         <v>1354</v>
       </c>
-      <c r="C473" s="111" t="s">
-        <v>1259</v>
+      <c r="C473" s="117" t="s">
+        <v>1256</v>
       </c>
       <c r="D473" s="111">
         <v>8</v>
@@ -47781,8 +47784,8 @@
       <c r="B474" s="114" t="s">
         <v>1358</v>
       </c>
-      <c r="C474" s="114" t="s">
-        <v>1250</v>
+      <c r="C474" s="118" t="s">
+        <v>1258</v>
       </c>
       <c r="D474" s="114">
         <v>8</v>

--- a/DA PORTAL.xlsx
+++ b/DA PORTAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\downlodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EBFC902-4386-48C9-9887-E89DF0882445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2075DB2D-258A-47BA-A57F-04288A0B9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15510" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15510" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONAL INFORMATION" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9165" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9765" uniqueCount="1443">
   <si>
     <t>Name</t>
   </si>
@@ -4145,6 +4145,252 @@
   </si>
   <si>
     <t>Intern Project</t>
+  </si>
+  <si>
+    <t>ABI S A RAJAN</t>
+  </si>
+  <si>
+    <t>ABIRAJAN14042002@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ST. PETER'S COLLEGE</t>
+  </si>
+  <si>
+    <t>13.10.2025</t>
+  </si>
+  <si>
+    <t>19.12.2025</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>AJAIKUMAR V</t>
+  </si>
+  <si>
+    <t>AJAIKUMAR12C@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ATCHAYA SRITHAR</t>
+  </si>
+  <si>
+    <t>ATCHUSRITHAR@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AYYAPPAN M</t>
+  </si>
+  <si>
+    <t>AYYAPPANMANI05555@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DEEPA L</t>
+  </si>
+  <si>
+    <t>DEEPA021019@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DIVAKAR</t>
+  </si>
+  <si>
+    <t>DIVAJAGAN1370@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRIRAM COLLEGE</t>
+  </si>
+  <si>
+    <t>DIVYA</t>
+  </si>
+  <si>
+    <t>DIVYAVENKATESAN653@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HARSINI S</t>
+  </si>
+  <si>
+    <t>HARSINI0510@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>B.E</t>
+  </si>
+  <si>
+    <t>ARAVIND</t>
+  </si>
+  <si>
+    <t>IARAVIND679@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JAYAVIGNESH</t>
+  </si>
+  <si>
+    <t>JAIVIGNESHVIGNESH3@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JEPPIAAR COLLEGE OD ARTS AND SCIENCE</t>
+  </si>
+  <si>
+    <t>BBA</t>
+  </si>
+  <si>
+    <t>JASSIM I</t>
+  </si>
+  <si>
+    <t>JASSIM16021234@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>B.TECH ECE</t>
+  </si>
+  <si>
+    <t>JUDITH LYNN J</t>
+  </si>
+  <si>
+    <t>JUDYJJTHOMAS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VELTECH RANGA SANKU ARTS COLLEGE UNIVERSITY</t>
+  </si>
+  <si>
+    <t>KARTHIKEYAN K</t>
+  </si>
+  <si>
+    <t>KARTHIKEYAN3032K@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HINDUSTAN INSTITUTE OF SCIENCE AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>LAVANYA A</t>
+  </si>
+  <si>
+    <t>LAVIANJI2@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LOGESH A</t>
+  </si>
+  <si>
+    <t>LOGESHANNAMALAI12@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DR SNS RAJALAKSHMI ARTS AND SCIENCE</t>
+  </si>
+  <si>
+    <t>LOKHALAKSHMI A</t>
+  </si>
+  <si>
+    <t>LOKHAANNAMALAI@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MEENAKSHI COLLEGE</t>
+  </si>
+  <si>
+    <t>NARMADHA</t>
+  </si>
+  <si>
+    <t>MYSELFNARMADHA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRAAVYA N</t>
+  </si>
+  <si>
+    <t>NSRAAVYA1@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VELAMMAL INSTTUTE OF TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>RAMYALAKSHMI</t>
+  </si>
+  <si>
+    <t>RAMYALAKSHMIRL2000@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GOVINDAMMAL ADITANAR COLLEGE FOR WOMEN</t>
+  </si>
+  <si>
+    <t>NAFFISHA RIZHWANA N</t>
+  </si>
+  <si>
+    <t>RIZHWANA2004@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SARAN JOSEPH</t>
+  </si>
+  <si>
+    <t>SARANJOSEPHEASWARVEL@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BE. MECH</t>
+  </si>
+  <si>
+    <t>SAKTHI A</t>
+  </si>
+  <si>
+    <t>SHAKTHIDAYANITHI04@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>B.S.ABDUR CRESCENT INSTITUTE OF SCIENCE AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>YOGALAKSHMI M</t>
+  </si>
+  <si>
+    <t>SKY.SANAVUBS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MSC PHYSICS</t>
+  </si>
+  <si>
+    <t>SUBANESH D</t>
+  </si>
+  <si>
+    <t>SUBANESHDHAYALAN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BHARATH INSTITUTE OF HIGHER EDUCATION AND RESEARCH</t>
+  </si>
+  <si>
+    <t>VENKATVICKY764@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRI MUTHUKUMARAN INSTITUTE OF TECHONOLOGY</t>
+  </si>
+  <si>
+    <t>BE ECE</t>
+  </si>
+  <si>
+    <t>VIJAY R</t>
+  </si>
+  <si>
+    <t>vijay110305@gmail.com</t>
+  </si>
+  <si>
+    <t>AVICHI COLLEGE OF ARTS AND SCIENCE</t>
+  </si>
+  <si>
+    <t>VINODHA R</t>
+  </si>
+  <si>
+    <t>VINOTHA8838@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>POOVIZHI P</t>
+  </si>
+  <si>
+    <t>VIZHI1001@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KAVIPRABHA</t>
+  </si>
+  <si>
+    <t>WRITETOKAVIPRABHA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>Dr.N.G.P Arts and Science College</t>
+  </si>
+  <si>
+    <t>YOGESH KANNA K</t>
+  </si>
+  <si>
+    <t>YOGESHKANNA95@GMAIL.COM</t>
   </si>
 </sst>
 </file>
@@ -4511,7 +4757,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -4850,6 +5096,12 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5115,7 +5367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N472"/>
+  <dimension ref="A1:N503"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="77"/>
@@ -25306,6 +25558,1327 @@
         <v>1266</v>
       </c>
     </row>
+    <row r="473" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="474" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A474" s="107" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B474" s="108" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C474" s="108">
+        <v>9150138937</v>
+      </c>
+      <c r="D474" s="108" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E474" s="108" t="s">
+        <v>54</v>
+      </c>
+      <c r="F474" s="109">
+        <v>45918</v>
+      </c>
+      <c r="G474" s="108" t="s">
+        <v>18</v>
+      </c>
+      <c r="H474" s="108" t="s">
+        <v>19</v>
+      </c>
+      <c r="I474" s="108" t="s">
+        <v>680</v>
+      </c>
+      <c r="J474" s="108" t="s">
+        <v>953</v>
+      </c>
+      <c r="K474" s="108" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L474" s="108" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M474" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="N474" s="108" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="475" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A475" s="110" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B475" s="111" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C475" s="111">
+        <v>6381941954</v>
+      </c>
+      <c r="D475" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="E475" s="111" t="s">
+        <v>54</v>
+      </c>
+      <c r="F475" s="112">
+        <v>45927</v>
+      </c>
+      <c r="G475" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H475" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I475" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J475" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K475" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L475" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M475" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N475" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="476" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A476" s="113" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B476" s="114" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C476" s="114">
+        <v>8825912604</v>
+      </c>
+      <c r="D476" s="114" t="s">
+        <v>710</v>
+      </c>
+      <c r="E476" s="114" t="s">
+        <v>332</v>
+      </c>
+      <c r="F476" s="115">
+        <v>45922</v>
+      </c>
+      <c r="G476" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H476" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I476" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J476" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K476" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L476" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M476" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N476" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="477" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="110" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B477" s="111" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C477" s="111">
+        <v>7550065890</v>
+      </c>
+      <c r="D477" s="111" t="s">
+        <v>539</v>
+      </c>
+      <c r="E477" s="111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F477" s="112">
+        <v>45929</v>
+      </c>
+      <c r="G477" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H477" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I477" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J477" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K477" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L477" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M477" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N477" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="478" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="113" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B478" s="114" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C478" s="114">
+        <v>9043217682</v>
+      </c>
+      <c r="D478" s="114" t="s">
+        <v>425</v>
+      </c>
+      <c r="E478" s="114" t="s">
+        <v>43</v>
+      </c>
+      <c r="F478" s="115">
+        <v>45918</v>
+      </c>
+      <c r="G478" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H478" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I478" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J478" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K478" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L478" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M478" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N478" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="479" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="110" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B479" s="111" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C479" s="111">
+        <v>7339062158</v>
+      </c>
+      <c r="D479" s="111" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E479" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="F479" s="112">
+        <v>45883</v>
+      </c>
+      <c r="G479" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H479" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I479" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J479" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K479" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L479" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M479" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N479" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="480" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="113" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B480" s="114" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C480" s="114">
+        <v>7806863463</v>
+      </c>
+      <c r="D480" s="114" t="s">
+        <v>710</v>
+      </c>
+      <c r="E480" s="114" t="s">
+        <v>332</v>
+      </c>
+      <c r="F480" s="115">
+        <v>45922</v>
+      </c>
+      <c r="G480" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H480" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I480" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J480" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K480" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L480" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M480" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N480" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="481" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="110" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B481" s="111" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C481" s="111">
+        <v>6385460510</v>
+      </c>
+      <c r="D481" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="E481" s="111" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F481" s="112">
+        <v>45922</v>
+      </c>
+      <c r="G481" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H481" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I481" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J481" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K481" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L481" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M481" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N481" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="482" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="113" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B482" s="114" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C482" s="114">
+        <v>8754781384</v>
+      </c>
+      <c r="D482" s="114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E482" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F482" s="115">
+        <v>45933</v>
+      </c>
+      <c r="G482" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H482" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I482" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J482" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K482" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L482" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M482" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N482" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="483" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="110" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B483" s="111" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C483" s="111">
+        <v>9884194999</v>
+      </c>
+      <c r="D483" s="111" t="s">
+        <v>1387</v>
+      </c>
+      <c r="E483" s="111" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F483" s="112">
+        <v>45918</v>
+      </c>
+      <c r="G483" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H483" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I483" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J483" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K483" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L483" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M483" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N483" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="484" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="113" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B484" s="114" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C484" s="114">
+        <v>9345795787</v>
+      </c>
+      <c r="D484" s="114" t="s">
+        <v>151</v>
+      </c>
+      <c r="E484" s="114" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F484" s="115">
+        <v>45920</v>
+      </c>
+      <c r="G484" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H484" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I484" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J484" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K484" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L484" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M484" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N484" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="485" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A485" s="110" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B485" s="111" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C485" s="111">
+        <v>7339631996</v>
+      </c>
+      <c r="D485" s="111" t="s">
+        <v>1394</v>
+      </c>
+      <c r="E485" s="111" t="s">
+        <v>241</v>
+      </c>
+      <c r="F485" s="112">
+        <v>45912</v>
+      </c>
+      <c r="G485" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H485" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I485" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J485" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K485" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L485" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M485" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N485" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="486" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="113" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B486" s="114" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C486" s="114">
+        <v>8778212605</v>
+      </c>
+      <c r="D486" s="114" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E486" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F486" s="115">
+        <v>45915</v>
+      </c>
+      <c r="G486" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H486" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I486" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J486" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K486" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L486" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M486" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N486" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="487" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="110" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B487" s="111" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C487" s="111">
+        <v>7448786837</v>
+      </c>
+      <c r="D487" s="111" t="s">
+        <v>222</v>
+      </c>
+      <c r="E487" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="F487" s="112">
+        <v>45917</v>
+      </c>
+      <c r="G487" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H487" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I487" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J487" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K487" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L487" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M487" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N487" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="488" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="113" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B488" s="114" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C488" s="114">
+        <v>6379257019</v>
+      </c>
+      <c r="D488" s="114" t="s">
+        <v>1402</v>
+      </c>
+      <c r="E488" s="114" t="s">
+        <v>241</v>
+      </c>
+      <c r="F488" s="115">
+        <v>45915</v>
+      </c>
+      <c r="G488" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H488" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I488" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J488" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K488" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L488" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M488" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N488" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="489" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="110" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B489" s="111" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C489" s="111">
+        <v>9361853550</v>
+      </c>
+      <c r="D489" s="111" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E489" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F489" s="112">
+        <v>45926</v>
+      </c>
+      <c r="G489" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H489" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I489" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J489" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K489" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L489" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M489" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N489" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="490" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="113" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B490" s="114" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C490" s="114">
+        <v>9080491156</v>
+      </c>
+      <c r="D490" s="114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E490" s="114" t="s">
+        <v>75</v>
+      </c>
+      <c r="F490" s="115">
+        <v>45920</v>
+      </c>
+      <c r="G490" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H490" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I490" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J490" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K490" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L490" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M490" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N490" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="491" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="110" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B491" s="111" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C491" s="111">
+        <v>7010425124</v>
+      </c>
+      <c r="D491" s="111" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E491" s="111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F491" s="112">
+        <v>45943</v>
+      </c>
+      <c r="G491" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H491" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I491" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J491" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K491" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L491" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M491" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N491" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="492" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="113" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B492" s="114" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C492" s="114">
+        <v>7358433202</v>
+      </c>
+      <c r="D492" s="114" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E492" s="114" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F492" s="115">
+        <v>45920</v>
+      </c>
+      <c r="G492" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H492" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I492" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J492" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K492" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L492" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M492" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N492" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="493" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="110" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B493" s="111" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C493" s="111">
+        <v>7904546194</v>
+      </c>
+      <c r="D493" s="111" t="s">
+        <v>1021</v>
+      </c>
+      <c r="E493" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="F493" s="112">
+        <v>45920</v>
+      </c>
+      <c r="G493" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H493" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I493" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J493" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K493" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L493" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M493" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N493" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="494" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="113" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B494" s="114" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C494" s="114">
+        <v>9384659097</v>
+      </c>
+      <c r="D494" s="114" t="s">
+        <v>78</v>
+      </c>
+      <c r="E494" s="114" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F494" s="115">
+        <v>45912</v>
+      </c>
+      <c r="G494" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H494" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I494" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J494" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K494" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L494" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M494" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N494" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="495" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="110" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B495" s="111" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C495" s="111">
+        <v>7358598754</v>
+      </c>
+      <c r="D495" s="111" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E495" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F495" s="112">
+        <v>45934</v>
+      </c>
+      <c r="G495" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H495" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I495" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J495" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K495" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L495" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M495" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N495" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="496" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="113" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B496" s="114" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C496" s="114">
+        <v>7397762918</v>
+      </c>
+      <c r="D496" s="114" t="s">
+        <v>1413</v>
+      </c>
+      <c r="E496" s="114" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F496" s="115">
+        <v>45919</v>
+      </c>
+      <c r="G496" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H496" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I496" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J496" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K496" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L496" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M496" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N496" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="497" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="110" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B497" s="111" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C497" s="111">
+        <v>9345767906</v>
+      </c>
+      <c r="D497" s="111" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E497" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F497" s="112">
+        <v>45912</v>
+      </c>
+      <c r="G497" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H497" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I497" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J497" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K497" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L497" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M497" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N497" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="498" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="113" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B498" s="114" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C498" s="114">
+        <v>7010922285</v>
+      </c>
+      <c r="D498" s="114" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E498" s="114" t="s">
+        <v>1430</v>
+      </c>
+      <c r="F498" s="115">
+        <v>45929</v>
+      </c>
+      <c r="G498" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H498" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I498" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J498" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K498" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L498" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M498" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N498" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="499" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="110" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B499" s="111" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C499" s="111">
+        <v>7305604526</v>
+      </c>
+      <c r="D499" s="111" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E499" s="111" t="s">
+        <v>790</v>
+      </c>
+      <c r="F499" s="112">
+        <v>45937</v>
+      </c>
+      <c r="G499" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H499" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I499" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J499" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K499" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L499" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M499" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N499" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="500" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="113" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B500" s="114" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C500" s="114">
+        <v>8838589378</v>
+      </c>
+      <c r="D500" s="114" t="s">
+        <v>250</v>
+      </c>
+      <c r="E500" s="114" t="s">
+        <v>75</v>
+      </c>
+      <c r="F500" s="115">
+        <v>45920</v>
+      </c>
+      <c r="G500" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H500" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I500" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J500" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K500" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L500" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M500" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N500" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="501" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="110" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B501" s="111" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C501" s="111">
+        <v>6369865254</v>
+      </c>
+      <c r="D501" s="111" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E501" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F501" s="112">
+        <v>45934</v>
+      </c>
+      <c r="G501" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H501" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I501" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J501" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K501" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L501" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M501" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N501" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="502" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="113" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B502" s="114" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C502" s="114">
+        <v>9688196238</v>
+      </c>
+      <c r="D502" s="114" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E502" s="114" t="s">
+        <v>831</v>
+      </c>
+      <c r="F502" s="115">
+        <v>45923</v>
+      </c>
+      <c r="G502" s="114" t="s">
+        <v>18</v>
+      </c>
+      <c r="H502" s="114" t="s">
+        <v>19</v>
+      </c>
+      <c r="I502" s="114" t="s">
+        <v>680</v>
+      </c>
+      <c r="J502" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K502" s="114" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L502" s="114" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M502" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N502" s="114" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="503" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="110" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B503" s="111" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C503" s="111">
+        <v>9080357363</v>
+      </c>
+      <c r="D503" s="111" t="s">
+        <v>570</v>
+      </c>
+      <c r="E503" s="111" t="s">
+        <v>75</v>
+      </c>
+      <c r="F503" s="112">
+        <v>45927</v>
+      </c>
+      <c r="G503" s="111" t="s">
+        <v>18</v>
+      </c>
+      <c r="H503" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I503" s="111" t="s">
+        <v>680</v>
+      </c>
+      <c r="J503" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K503" s="111" t="s">
+        <v>1364</v>
+      </c>
+      <c r="L503" s="111" t="s">
+        <v>1365</v>
+      </c>
+      <c r="M503" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N503" s="111" t="s">
+        <v>1366</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -25314,7 +26887,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F474"/>
+  <dimension ref="A1:F506"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="55" customWidth="1"/>
@@ -33122,6 +34695,517 @@
         <v>1266</v>
       </c>
     </row>
+    <row r="476" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="477" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A477" s="107" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B477" s="108">
+        <v>90</v>
+      </c>
+      <c r="C477" s="116" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D477" s="116" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E477" s="120" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A478" s="110" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B478" s="111">
+        <v>50</v>
+      </c>
+      <c r="C478" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D478" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E478" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A479" s="113" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B479" s="114">
+        <v>80</v>
+      </c>
+      <c r="C479" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D479" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E479" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A480" s="110" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B480" s="111">
+        <v>70</v>
+      </c>
+      <c r="C480" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D480" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E480" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A481" s="113" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B481" s="114">
+        <v>70</v>
+      </c>
+      <c r="C481" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D481" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E481" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A482" s="110" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B482" s="111">
+        <v>70</v>
+      </c>
+      <c r="C482" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D482" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E482" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A483" s="113" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B483" s="114">
+        <v>80</v>
+      </c>
+      <c r="C483" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D483" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E483" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A484" s="110" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B484" s="111">
+        <v>75</v>
+      </c>
+      <c r="C484" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D484" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E484" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A485" s="113" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B485" s="114">
+        <v>80</v>
+      </c>
+      <c r="C485" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D485" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E485" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A486" s="110" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B486" s="111">
+        <v>60</v>
+      </c>
+      <c r="C486" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D486" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E486" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A487" s="113" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B487" s="114">
+        <v>70</v>
+      </c>
+      <c r="C487" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D487" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E487" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A488" s="110" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B488" s="111">
+        <v>85</v>
+      </c>
+      <c r="C488" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D488" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E488" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A489" s="113" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B489" s="114">
+        <v>50</v>
+      </c>
+      <c r="C489" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D489" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E489" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A490" s="110" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B490" s="111">
+        <v>70</v>
+      </c>
+      <c r="C490" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D490" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E490" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A491" s="113" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B491" s="114">
+        <v>65</v>
+      </c>
+      <c r="C491" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D491" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E491" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A492" s="110" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B492" s="111">
+        <v>90</v>
+      </c>
+      <c r="C492" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D492" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E492" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A493" s="113" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B493" s="114">
+        <v>75</v>
+      </c>
+      <c r="C493" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D493" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E493" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A494" s="110" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B494" s="111">
+        <v>90</v>
+      </c>
+      <c r="C494" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D494" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E494" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A495" s="113" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B495" s="114">
+        <v>85</v>
+      </c>
+      <c r="C495" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D495" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E495" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A496" s="110" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B496" s="111">
+        <v>60</v>
+      </c>
+      <c r="C496" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D496" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E496" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A497" s="113" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B497" s="114">
+        <v>80</v>
+      </c>
+      <c r="C497" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D497" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E497" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A498" s="110" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B498" s="111">
+        <v>85</v>
+      </c>
+      <c r="C498" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D498" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E498" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A499" s="113" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B499" s="114">
+        <v>80</v>
+      </c>
+      <c r="C499" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D499" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E499" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A500" s="110" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B500" s="111">
+        <v>85</v>
+      </c>
+      <c r="C500" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D500" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E500" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A501" s="113" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B501" s="114">
+        <v>70</v>
+      </c>
+      <c r="C501" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D501" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E501" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A502" s="110" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B502" s="111">
+        <v>80</v>
+      </c>
+      <c r="C502" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D502" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E502" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A503" s="113" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B503" s="114">
+        <v>60</v>
+      </c>
+      <c r="C503" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D503" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E503" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A504" s="110" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B504" s="111">
+        <v>75</v>
+      </c>
+      <c r="C504" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D504" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E504" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A505" s="113" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B505" s="114">
+        <v>80</v>
+      </c>
+      <c r="C505" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D505" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E505" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A506" s="110" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B506" s="111">
+        <v>85</v>
+      </c>
+      <c r="C506" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D506" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E506" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A29" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -33133,7 +35217,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J474"/>
+  <dimension ref="A1:J506"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="2" customWidth="1"/>
@@ -47809,6 +49893,967 @@
         <v>1266</v>
       </c>
     </row>
+    <row r="476" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="477" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A477" s="107" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B477" s="108" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C477" s="108" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D477" s="108">
+        <v>8</v>
+      </c>
+      <c r="E477" s="108">
+        <v>8</v>
+      </c>
+      <c r="F477" s="108">
+        <v>8</v>
+      </c>
+      <c r="G477" s="108">
+        <v>8</v>
+      </c>
+      <c r="H477" s="108">
+        <v>7</v>
+      </c>
+      <c r="I477" s="108">
+        <v>39</v>
+      </c>
+      <c r="J477" s="120" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="478" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A478" s="110" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B478" s="111" t="s">
+        <v>1368</v>
+      </c>
+      <c r="C478" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D478" s="111">
+        <v>6</v>
+      </c>
+      <c r="E478" s="111">
+        <v>5</v>
+      </c>
+      <c r="F478" s="111">
+        <v>6</v>
+      </c>
+      <c r="G478" s="111">
+        <v>4</v>
+      </c>
+      <c r="H478" s="111">
+        <v>4</v>
+      </c>
+      <c r="I478" s="111">
+        <v>25</v>
+      </c>
+      <c r="J478" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="479" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A479" s="113" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B479" s="114" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C479" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D479" s="114">
+        <v>6</v>
+      </c>
+      <c r="E479" s="114">
+        <v>6</v>
+      </c>
+      <c r="F479" s="114">
+        <v>7</v>
+      </c>
+      <c r="G479" s="114">
+        <v>4</v>
+      </c>
+      <c r="H479" s="114">
+        <v>4</v>
+      </c>
+      <c r="I479" s="114">
+        <v>27</v>
+      </c>
+      <c r="J479" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="480" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A480" s="110" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B480" s="111" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C480" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D480" s="111">
+        <v>7</v>
+      </c>
+      <c r="E480" s="111">
+        <v>6</v>
+      </c>
+      <c r="F480" s="111">
+        <v>7</v>
+      </c>
+      <c r="G480" s="111">
+        <v>4</v>
+      </c>
+      <c r="H480" s="111">
+        <v>4</v>
+      </c>
+      <c r="I480" s="111">
+        <v>28</v>
+      </c>
+      <c r="J480" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="481" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A481" s="113" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B481" s="114" t="s">
+        <v>1374</v>
+      </c>
+      <c r="C481" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D481" s="114">
+        <v>6</v>
+      </c>
+      <c r="E481" s="114">
+        <v>7</v>
+      </c>
+      <c r="F481" s="114">
+        <v>6</v>
+      </c>
+      <c r="G481" s="114">
+        <v>4</v>
+      </c>
+      <c r="H481" s="114">
+        <v>4</v>
+      </c>
+      <c r="I481" s="114">
+        <v>27</v>
+      </c>
+      <c r="J481" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="482" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A482" s="110" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B482" s="111" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C482" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D482" s="111">
+        <v>7</v>
+      </c>
+      <c r="E482" s="111">
+        <v>6</v>
+      </c>
+      <c r="F482" s="111">
+        <v>5</v>
+      </c>
+      <c r="G482" s="111">
+        <v>4</v>
+      </c>
+      <c r="H482" s="111">
+        <v>4</v>
+      </c>
+      <c r="I482" s="111">
+        <v>26</v>
+      </c>
+      <c r="J482" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="483" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A483" s="113" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B483" s="114" t="s">
+        <v>1379</v>
+      </c>
+      <c r="C483" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D483" s="114">
+        <v>7</v>
+      </c>
+      <c r="E483" s="114">
+        <v>7.5</v>
+      </c>
+      <c r="F483" s="114">
+        <v>6.5</v>
+      </c>
+      <c r="G483" s="114">
+        <v>4</v>
+      </c>
+      <c r="H483" s="114">
+        <v>4</v>
+      </c>
+      <c r="I483" s="114">
+        <v>29</v>
+      </c>
+      <c r="J483" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="484" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A484" s="110" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B484" s="111" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C484" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D484" s="111">
+        <v>7</v>
+      </c>
+      <c r="E484" s="111">
+        <v>6</v>
+      </c>
+      <c r="F484" s="111">
+        <v>5</v>
+      </c>
+      <c r="G484" s="111">
+        <v>4</v>
+      </c>
+      <c r="H484" s="111">
+        <v>4</v>
+      </c>
+      <c r="I484" s="111">
+        <v>26</v>
+      </c>
+      <c r="J484" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="485" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A485" s="113" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B485" s="114" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C485" s="114" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D485" s="114">
+        <v>8</v>
+      </c>
+      <c r="E485" s="114">
+        <v>7</v>
+      </c>
+      <c r="F485" s="114">
+        <v>7</v>
+      </c>
+      <c r="G485" s="114">
+        <v>4</v>
+      </c>
+      <c r="H485" s="114">
+        <v>4</v>
+      </c>
+      <c r="I485" s="114">
+        <v>30</v>
+      </c>
+      <c r="J485" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="486" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="110" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B486" s="111" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C486" s="111" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D486" s="111">
+        <v>7</v>
+      </c>
+      <c r="E486" s="111">
+        <v>6</v>
+      </c>
+      <c r="F486" s="111">
+        <v>5.5</v>
+      </c>
+      <c r="G486" s="111">
+        <v>4</v>
+      </c>
+      <c r="H486" s="111">
+        <v>4</v>
+      </c>
+      <c r="I486" s="111">
+        <v>26.5</v>
+      </c>
+      <c r="J486" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="487" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="113" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B487" s="114" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C487" s="114" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D487" s="114">
+        <v>7</v>
+      </c>
+      <c r="E487" s="114">
+        <v>6</v>
+      </c>
+      <c r="F487" s="114">
+        <v>7</v>
+      </c>
+      <c r="G487" s="114">
+        <v>4</v>
+      </c>
+      <c r="H487" s="114">
+        <v>4</v>
+      </c>
+      <c r="I487" s="114">
+        <v>28</v>
+      </c>
+      <c r="J487" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="488" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="110" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B488" s="111" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C488" s="111" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D488" s="111">
+        <v>8</v>
+      </c>
+      <c r="E488" s="111">
+        <v>7</v>
+      </c>
+      <c r="F488" s="111">
+        <v>8</v>
+      </c>
+      <c r="G488" s="111">
+        <v>4</v>
+      </c>
+      <c r="H488" s="111">
+        <v>4</v>
+      </c>
+      <c r="I488" s="111">
+        <v>31</v>
+      </c>
+      <c r="J488" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="489" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="113" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B489" s="114" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C489" s="114" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D489" s="114">
+        <v>6</v>
+      </c>
+      <c r="E489" s="114">
+        <v>6</v>
+      </c>
+      <c r="F489" s="114">
+        <v>5</v>
+      </c>
+      <c r="G489" s="114">
+        <v>4</v>
+      </c>
+      <c r="H489" s="114">
+        <v>4</v>
+      </c>
+      <c r="I489" s="114">
+        <v>25</v>
+      </c>
+      <c r="J489" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="490" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="110" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B490" s="111" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C490" s="111" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D490" s="111">
+        <v>7</v>
+      </c>
+      <c r="E490" s="111">
+        <v>6</v>
+      </c>
+      <c r="F490" s="111">
+        <v>5</v>
+      </c>
+      <c r="G490" s="111">
+        <v>7</v>
+      </c>
+      <c r="H490" s="111">
+        <v>7</v>
+      </c>
+      <c r="I490" s="111">
+        <v>32</v>
+      </c>
+      <c r="J490" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="491" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="113" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B491" s="114" t="s">
+        <v>1401</v>
+      </c>
+      <c r="C491" s="114" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D491" s="114">
+        <v>6</v>
+      </c>
+      <c r="E491" s="114">
+        <v>7</v>
+      </c>
+      <c r="F491" s="114">
+        <v>7</v>
+      </c>
+      <c r="G491" s="114">
+        <v>4</v>
+      </c>
+      <c r="H491" s="114">
+        <v>4</v>
+      </c>
+      <c r="I491" s="114">
+        <v>28</v>
+      </c>
+      <c r="J491" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="492" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="110" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B492" s="111" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C492" s="111" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D492" s="111">
+        <v>7</v>
+      </c>
+      <c r="E492" s="111">
+        <v>8</v>
+      </c>
+      <c r="F492" s="111">
+        <v>7</v>
+      </c>
+      <c r="G492" s="111">
+        <v>4</v>
+      </c>
+      <c r="H492" s="111">
+        <v>4</v>
+      </c>
+      <c r="I492" s="111">
+        <v>30</v>
+      </c>
+      <c r="J492" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="493" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="113" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B493" s="114" t="s">
+        <v>1407</v>
+      </c>
+      <c r="C493" s="114" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D493" s="114">
+        <v>6</v>
+      </c>
+      <c r="E493" s="114">
+        <v>5</v>
+      </c>
+      <c r="F493" s="114">
+        <v>6</v>
+      </c>
+      <c r="G493" s="114">
+        <v>4</v>
+      </c>
+      <c r="H493" s="114">
+        <v>4</v>
+      </c>
+      <c r="I493" s="114">
+        <v>25</v>
+      </c>
+      <c r="J493" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="494" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="110" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B494" s="111" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C494" s="111" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D494" s="111">
+        <v>7</v>
+      </c>
+      <c r="E494" s="111">
+        <v>8</v>
+      </c>
+      <c r="F494" s="111">
+        <v>7</v>
+      </c>
+      <c r="G494" s="111">
+        <v>5</v>
+      </c>
+      <c r="H494" s="111">
+        <v>5</v>
+      </c>
+      <c r="I494" s="111">
+        <v>32</v>
+      </c>
+      <c r="J494" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="495" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="113" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B495" s="114" t="s">
+        <v>1412</v>
+      </c>
+      <c r="C495" s="114" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D495" s="114">
+        <v>8</v>
+      </c>
+      <c r="E495" s="114">
+        <v>7</v>
+      </c>
+      <c r="F495" s="114">
+        <v>6</v>
+      </c>
+      <c r="G495" s="114">
+        <v>4</v>
+      </c>
+      <c r="H495" s="114">
+        <v>4</v>
+      </c>
+      <c r="I495" s="114">
+        <v>29</v>
+      </c>
+      <c r="J495" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="496" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A496" s="110" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B496" s="111" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C496" s="111" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D496" s="111">
+        <v>7</v>
+      </c>
+      <c r="E496" s="111">
+        <v>7</v>
+      </c>
+      <c r="F496" s="111">
+        <v>6</v>
+      </c>
+      <c r="G496" s="111">
+        <v>4</v>
+      </c>
+      <c r="H496" s="111">
+        <v>4</v>
+      </c>
+      <c r="I496" s="111">
+        <v>28</v>
+      </c>
+      <c r="J496" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="497" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A497" s="113" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B497" s="114" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C497" s="114" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D497" s="114">
+        <v>7</v>
+      </c>
+      <c r="E497" s="114">
+        <v>8</v>
+      </c>
+      <c r="F497" s="114">
+        <v>8</v>
+      </c>
+      <c r="G497" s="114">
+        <v>7</v>
+      </c>
+      <c r="H497" s="114">
+        <v>7</v>
+      </c>
+      <c r="I497" s="114">
+        <v>37</v>
+      </c>
+      <c r="J497" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="498" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A498" s="110" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B498" s="111" t="s">
+        <v>1420</v>
+      </c>
+      <c r="C498" s="111" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D498" s="111">
+        <v>8</v>
+      </c>
+      <c r="E498" s="111">
+        <v>7</v>
+      </c>
+      <c r="F498" s="111">
+        <v>7</v>
+      </c>
+      <c r="G498" s="111">
+        <v>4</v>
+      </c>
+      <c r="H498" s="111">
+        <v>4</v>
+      </c>
+      <c r="I498" s="111">
+        <v>30</v>
+      </c>
+      <c r="J498" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="499" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A499" s="113" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B499" s="114" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C499" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D499" s="114">
+        <v>7</v>
+      </c>
+      <c r="E499" s="114">
+        <v>7</v>
+      </c>
+      <c r="F499" s="114">
+        <v>6</v>
+      </c>
+      <c r="G499" s="114">
+        <v>4</v>
+      </c>
+      <c r="H499" s="114">
+        <v>4</v>
+      </c>
+      <c r="I499" s="114">
+        <v>28</v>
+      </c>
+      <c r="J499" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="500" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A500" s="110" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B500" s="111" t="s">
+        <v>1426</v>
+      </c>
+      <c r="C500" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D500" s="111">
+        <v>7</v>
+      </c>
+      <c r="E500" s="111">
+        <v>8</v>
+      </c>
+      <c r="F500" s="111">
+        <v>7</v>
+      </c>
+      <c r="G500" s="111">
+        <v>4</v>
+      </c>
+      <c r="H500" s="111">
+        <v>4</v>
+      </c>
+      <c r="I500" s="111">
+        <v>30</v>
+      </c>
+      <c r="J500" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="501" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A501" s="113" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B501" s="114" t="s">
+        <v>1428</v>
+      </c>
+      <c r="C501" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D501" s="114">
+        <v>7</v>
+      </c>
+      <c r="E501" s="114">
+        <v>7</v>
+      </c>
+      <c r="F501" s="114">
+        <v>7</v>
+      </c>
+      <c r="G501" s="114">
+        <v>4</v>
+      </c>
+      <c r="H501" s="114">
+        <v>4</v>
+      </c>
+      <c r="I501" s="114">
+        <v>29</v>
+      </c>
+      <c r="J501" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="502" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="110" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B502" s="111" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C502" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D502" s="111">
+        <v>7</v>
+      </c>
+      <c r="E502" s="111">
+        <v>8</v>
+      </c>
+      <c r="F502" s="111">
+        <v>7</v>
+      </c>
+      <c r="G502" s="111">
+        <v>4</v>
+      </c>
+      <c r="H502" s="111">
+        <v>4</v>
+      </c>
+      <c r="I502" s="111">
+        <v>30</v>
+      </c>
+      <c r="J502" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="113" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B503" s="114" t="s">
+        <v>1435</v>
+      </c>
+      <c r="C503" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D503" s="114">
+        <v>6</v>
+      </c>
+      <c r="E503" s="114">
+        <v>5</v>
+      </c>
+      <c r="F503" s="114">
+        <v>7</v>
+      </c>
+      <c r="G503" s="114">
+        <v>4</v>
+      </c>
+      <c r="H503" s="114">
+        <v>4</v>
+      </c>
+      <c r="I503" s="114">
+        <v>26</v>
+      </c>
+      <c r="J503" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="110" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B504" s="111" t="s">
+        <v>1437</v>
+      </c>
+      <c r="C504" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D504" s="111">
+        <v>7</v>
+      </c>
+      <c r="E504" s="111">
+        <v>6</v>
+      </c>
+      <c r="F504" s="111">
+        <v>6</v>
+      </c>
+      <c r="G504" s="111">
+        <v>4</v>
+      </c>
+      <c r="H504" s="111">
+        <v>4</v>
+      </c>
+      <c r="I504" s="111">
+        <v>27</v>
+      </c>
+      <c r="J504" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="113" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B505" s="114" t="s">
+        <v>1439</v>
+      </c>
+      <c r="C505" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D505" s="114">
+        <v>7</v>
+      </c>
+      <c r="E505" s="114">
+        <v>8</v>
+      </c>
+      <c r="F505" s="114">
+        <v>7</v>
+      </c>
+      <c r="G505" s="114">
+        <v>4</v>
+      </c>
+      <c r="H505" s="114">
+        <v>4</v>
+      </c>
+      <c r="I505" s="114">
+        <v>30</v>
+      </c>
+      <c r="J505" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="110" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B506" s="111" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C506" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D506" s="111">
+        <v>7</v>
+      </c>
+      <c r="E506" s="111">
+        <v>8</v>
+      </c>
+      <c r="F506" s="111">
+        <v>7</v>
+      </c>
+      <c r="G506" s="111">
+        <v>4</v>
+      </c>
+      <c r="H506" s="111">
+        <v>4</v>
+      </c>
+      <c r="I506" s="111">
+        <v>30</v>
+      </c>
+      <c r="J506" s="121" t="s">
+        <v>1366</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C352" r:id="rId1" tooltip="https://www.geeksforgeeks.org/data-science/market-basket-analysis-in-data-mining/" xr:uid="{00000000-0004-0000-0200-000000000000}"/>

--- a/DA PORTAL.xlsx
+++ b/DA PORTAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\downlodes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2075DB2D-258A-47BA-A57F-04288A0B9E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F6DAF7-5685-430B-B9C9-D666B5A15CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15510" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15510" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PERSONAL INFORMATION" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9765" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10625" uniqueCount="1561">
   <si>
     <t>Name</t>
   </si>
@@ -4391,6 +4391,360 @@
   </si>
   <si>
     <t>YOGESHKANNA95@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ROSHAN BERNARD A</t>
+  </si>
+  <si>
+    <t>0203roshanbernaard@gmail.com</t>
+  </si>
+  <si>
+    <t>03.11.2025</t>
+  </si>
+  <si>
+    <t>30.01.2026</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>RITHIKA V</t>
+  </si>
+  <si>
+    <t>AADHIRAIVIJAYANANTH@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SURYA GROUP OF INSTITUTIONS</t>
+  </si>
+  <si>
+    <t>SHAIK ABDULRAHEEM</t>
+  </si>
+  <si>
+    <t>ABDUL.SK1409@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GATE INSTITUTIONS</t>
+  </si>
+  <si>
+    <t>JEEVAN SIRAJ A</t>
+  </si>
+  <si>
+    <t>AJJEEVANS@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GR DAMODARAN COLLEGE OF ENGINEERING</t>
+  </si>
+  <si>
+    <t>JAIAKASH</t>
+  </si>
+  <si>
+    <t>AKASHZAKASH95@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KARPAGAM ACADEMY OF HIGHER EDUCATION</t>
+  </si>
+  <si>
+    <t>ALAGARASAN</t>
+  </si>
+  <si>
+    <t>ALAGARASANANBU@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SASTRA UNIVERSITY,THANJAVUR</t>
+  </si>
+  <si>
+    <t>MBA DATA ANALYTICS</t>
+  </si>
+  <si>
+    <t>ANANDHAVEL S</t>
+  </si>
+  <si>
+    <t>ANANDHAVEL2004@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>KARPAGAM INSTITUTE OF TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>ARSHIYA</t>
+  </si>
+  <si>
+    <t>ARSHIYAASAN2005@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AI DS</t>
+  </si>
+  <si>
+    <t>ARUN PRASADH A</t>
+  </si>
+  <si>
+    <t>ARUNPRASADH208@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AYILURI SIRISHA</t>
+  </si>
+  <si>
+    <t>AYILURISIRISHA@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BHARATH INSTITUTE OF HIGHER EDUCATION</t>
+  </si>
+  <si>
+    <t>CHARAN SAI</t>
+  </si>
+  <si>
+    <t>CSAI8609@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRINITHIY</t>
+  </si>
+  <si>
+    <t>DSRINITHIY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PSNA COLLEGE OF ENGINEERING</t>
+  </si>
+  <si>
+    <t>SANDHIYA D</t>
+  </si>
+  <si>
+    <t>DURAISANDHIYA623@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VENKATA SIVA REDDY</t>
+  </si>
+  <si>
+    <t>GADIKOTASIVAREDDY15@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GAYATHRI</t>
+  </si>
+  <si>
+    <t>GAYATHRIANBALAGAN111@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>GUNALAN</t>
+  </si>
+  <si>
+    <t>GUNALANV63@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VYASH TS</t>
+  </si>
+  <si>
+    <t>GURUVYASH@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>HARI PRASATH</t>
+  </si>
+  <si>
+    <t>HARIPRASATH2485@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>BSC DA</t>
+  </si>
+  <si>
+    <t>IKSHITHA</t>
+  </si>
+  <si>
+    <t>IKSHITHASENTHIL1602@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JAI GANESH K</t>
+  </si>
+  <si>
+    <t>JAIGA262002@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ME CSE</t>
+  </si>
+  <si>
+    <t>JITHESH KUMAR</t>
+  </si>
+  <si>
+    <t>JITESH.KUMAR2811@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>CSE (CYBER SECURITY)</t>
+  </si>
+  <si>
+    <t>KANMANI</t>
+  </si>
+  <si>
+    <t>KANMANINU@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SASTRA DEEMED TO BE UNIVERSITY</t>
+  </si>
+  <si>
+    <t>KOWSALYA</t>
+  </si>
+  <si>
+    <t>KOWSALYAKOWSY516@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LEENA</t>
+  </si>
+  <si>
+    <t>LEENAROYE2001@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>QUEEN MARY COLLEGE</t>
+  </si>
+  <si>
+    <t>LOKESH</t>
+  </si>
+  <si>
+    <t>LOKESHTHIRU1928@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRM ARTS AND SCINCE COLLEGE</t>
+  </si>
+  <si>
+    <t>MADHU METHA M</t>
+  </si>
+  <si>
+    <t>MADHUMITHAM911@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DHANRAJ BAID JAIN COLLEGE</t>
+  </si>
+  <si>
+    <t>SAI MANVISH CHOWDARY</t>
+  </si>
+  <si>
+    <t>MANVISHCHOWDARYIN@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>MEGALA</t>
+  </si>
+  <si>
+    <t>MEGALA160804@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ER. PERUMAL MANIMEKALAI COLLEGE OF ENGINEERING</t>
+  </si>
+  <si>
+    <t>THALLA YASWANTH REDDY</t>
+  </si>
+  <si>
+    <t>NERUALYASWANTHREDDY@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AUDISANKARA GROUP OF INSTITUTIONS AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>JAYANHANTHINI</t>
+  </si>
+  <si>
+    <t>NHANDHU05@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NIKITHA M</t>
+  </si>
+  <si>
+    <t>NIKITHAAMANICKAM@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>LADY DOAK COLLEGE</t>
+  </si>
+  <si>
+    <t>PRASANA KUMAR</t>
+  </si>
+  <si>
+    <t>PRASANAKUMAR0902@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>PRAVEENKUMAR</t>
+  </si>
+  <si>
+    <t>preveenkumar171@gmail.com</t>
+  </si>
+  <si>
+    <t>CHEMICAL</t>
+  </si>
+  <si>
+    <t>RAJESH M</t>
+  </si>
+  <si>
+    <t>RAJESHXM800@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JERIN R</t>
+  </si>
+  <si>
+    <t>RJERIN548@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>NITHISHA</t>
+  </si>
+  <si>
+    <t>RNITHISHA311NITHI@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>DR.MGR UNIVERSITY</t>
+  </si>
+  <si>
+    <t>SATHYA NARAYANAN M</t>
+  </si>
+  <si>
+    <t>SATHYASAKTHISATHYA4@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRC CAMPUS,SASTRA UNIVERSITY</t>
+  </si>
+  <si>
+    <t>B.SC CS</t>
+  </si>
+  <si>
+    <t>SHAIK KHALEEL BASHA</t>
+  </si>
+  <si>
+    <t>SHAIKKHALEEL1302@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>JAGAN'S COLLEGE OF ENGINEERING COLLEGE</t>
+  </si>
+  <si>
+    <t>JAWAHAR</t>
+  </si>
+  <si>
+    <t>SMJAWAI14PM@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>VENKATA SAI SOHITHA</t>
+  </si>
+  <si>
+    <t>SOHITHAMACHAVARAPU@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>ANNAMACHARYA INSTITUTE OF TECHNOLOGY AND SCIENCES</t>
+  </si>
+  <si>
+    <t>SRI AVINASH</t>
+  </si>
+  <si>
+    <t>SRIAVINASHSRIAVINASH@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>SRI MANAKULA VINAYAGAR ENG COLLEGE</t>
+  </si>
+  <si>
+    <t>SURUTHI S</t>
+  </si>
+  <si>
+    <t>SURUTHI.26CSB@LICET.AC.IN</t>
+  </si>
+  <si>
+    <t>LOYOLA ICAM COLLEGE OF ENGINEERING AND TECHNOLOGY</t>
+  </si>
+  <si>
+    <t>TANNU SHRI</t>
+  </si>
+  <si>
+    <t>TS3767@SRMIST.EDU.IN</t>
+  </si>
+  <si>
+    <t>SRM IST</t>
   </si>
 </sst>
 </file>
@@ -4757,7 +5111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -5102,6 +5456,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5367,7 +5733,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N503"/>
+  <dimension ref="A1:N547"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="77"/>
@@ -26879,6 +27245,1899 @@
         <v>1366</v>
       </c>
     </row>
+    <row r="504" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="505" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="107" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B505" s="108" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C505" s="108">
+        <v>9444034372</v>
+      </c>
+      <c r="D505" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="E505" s="108" t="s">
+        <v>37</v>
+      </c>
+      <c r="F505" s="109">
+        <v>45944</v>
+      </c>
+      <c r="G505" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="H505" s="120" t="s">
+        <v>19</v>
+      </c>
+      <c r="I505" s="122" t="s">
+        <v>724</v>
+      </c>
+      <c r="J505" s="108" t="s">
+        <v>953</v>
+      </c>
+      <c r="K505" s="108" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L505" s="108" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M505" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="N505" s="120" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="506" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="110" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B506" s="111" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C506" s="111">
+        <v>6385881750</v>
+      </c>
+      <c r="D506" s="111" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E506" s="111" t="s">
+        <v>29</v>
+      </c>
+      <c r="F506" s="112">
+        <v>45962</v>
+      </c>
+      <c r="G506" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H506" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I506" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J506" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K506" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L506" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M506" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N506" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="507" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="113" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B507" s="114" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C507" s="114">
+        <v>7337273935</v>
+      </c>
+      <c r="D507" s="114" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E507" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F507" s="115">
+        <v>45959</v>
+      </c>
+      <c r="G507" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H507" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I507" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J507" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K507" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L507" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M507" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N507" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="508" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="110" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B508" s="111" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C508" s="111">
+        <v>7708335584</v>
+      </c>
+      <c r="D508" s="111" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E508" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F508" s="112">
+        <v>45961</v>
+      </c>
+      <c r="G508" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H508" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I508" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J508" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K508" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L508" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M508" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N508" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="509" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="113" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B509" s="114" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C509" s="114">
+        <v>9025974909</v>
+      </c>
+      <c r="D509" s="114" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E509" s="114" t="s">
+        <v>321</v>
+      </c>
+      <c r="F509" s="115">
+        <v>45961</v>
+      </c>
+      <c r="G509" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H509" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I509" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J509" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K509" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L509" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M509" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N509" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="510" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="110" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B510" s="111" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C510" s="111">
+        <v>8838813034</v>
+      </c>
+      <c r="D510" s="111" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E510" s="111" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F510" s="112">
+        <v>45971</v>
+      </c>
+      <c r="G510" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H510" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I510" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J510" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K510" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L510" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M510" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N510" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="511" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="113" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B511" s="114" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C511" s="114">
+        <v>9443194738</v>
+      </c>
+      <c r="D511" s="114" t="s">
+        <v>1466</v>
+      </c>
+      <c r="E511" s="114" t="s">
+        <v>975</v>
+      </c>
+      <c r="F511" s="115">
+        <v>45947</v>
+      </c>
+      <c r="G511" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H511" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I511" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J511" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K511" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L511" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M511" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N511" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="512" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="110" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B512" s="111" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C512" s="111">
+        <v>9025617433</v>
+      </c>
+      <c r="D512" s="111" t="s">
+        <v>299</v>
+      </c>
+      <c r="E512" s="111" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F512" s="112">
+        <v>45948</v>
+      </c>
+      <c r="G512" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H512" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I512" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J512" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K512" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L512" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M512" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N512" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="513" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="113" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B513" s="114" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C513" s="114">
+        <v>9566973593</v>
+      </c>
+      <c r="D513" s="114" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E513" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F513" s="115">
+        <v>45961</v>
+      </c>
+      <c r="G513" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H513" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I513" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J513" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K513" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L513" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M513" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N513" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="514" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="110" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B514" s="111" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C514" s="111">
+        <v>6302683916</v>
+      </c>
+      <c r="D514" s="111" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E514" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="F514" s="112">
+        <v>45969</v>
+      </c>
+      <c r="G514" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H514" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I514" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J514" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K514" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L514" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M514" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N514" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="515" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="113" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B515" s="114" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C515" s="114">
+        <v>7893457925</v>
+      </c>
+      <c r="D515" s="114" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E515" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F515" s="115">
+        <v>45948</v>
+      </c>
+      <c r="G515" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H515" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I515" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J515" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K515" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L515" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M515" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N515" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="516" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="110" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B516" s="111" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C516" s="111">
+        <v>8122240287</v>
+      </c>
+      <c r="D516" s="111" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E516" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F516" s="112">
+        <v>45971</v>
+      </c>
+      <c r="G516" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H516" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I516" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J516" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K516" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L516" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M516" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N516" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="517" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="113" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B517" s="114" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C517" s="114">
+        <v>6385520901</v>
+      </c>
+      <c r="D517" s="114" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E517" s="114" t="s">
+        <v>29</v>
+      </c>
+      <c r="F517" s="115">
+        <v>45962</v>
+      </c>
+      <c r="G517" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H517" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I517" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J517" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K517" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L517" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M517" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N517" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="518" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="110" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B518" s="111" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C518" s="111">
+        <v>6301543121</v>
+      </c>
+      <c r="D518" s="111" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E518" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F518" s="112">
+        <v>45948</v>
+      </c>
+      <c r="G518" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H518" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I518" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J518" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K518" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L518" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M518" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N518" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="519" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="113" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B519" s="114" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C519" s="114">
+        <v>9600474158</v>
+      </c>
+      <c r="D519" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E519" s="114" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F519" s="115">
+        <v>45948</v>
+      </c>
+      <c r="G519" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H519" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I519" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J519" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K519" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L519" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M519" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N519" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="520" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="110" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B520" s="111" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C520" s="111">
+        <v>9566005901</v>
+      </c>
+      <c r="D520" s="111" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E520" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F520" s="112">
+        <v>45967</v>
+      </c>
+      <c r="G520" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H520" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I520" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J520" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K520" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L520" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M520" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N520" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="521" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="113" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B521" s="114" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C521" s="114">
+        <v>9344218083</v>
+      </c>
+      <c r="D521" s="114" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E521" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F521" s="115">
+        <v>45961</v>
+      </c>
+      <c r="G521" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H521" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I521" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J521" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K521" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L521" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M521" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N521" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="522" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="110" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B522" s="111" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C522" s="111">
+        <v>9566466568</v>
+      </c>
+      <c r="D522" s="111" t="s">
+        <v>1205</v>
+      </c>
+      <c r="E522" s="111" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F522" s="112">
+        <v>45954</v>
+      </c>
+      <c r="G522" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H522" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I522" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J522" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K522" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L522" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M522" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N522" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="523" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="113" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B523" s="114" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C523" s="114">
+        <v>9551645805</v>
+      </c>
+      <c r="D523" s="114" t="s">
+        <v>299</v>
+      </c>
+      <c r="E523" s="114" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F523" s="115">
+        <v>45948</v>
+      </c>
+      <c r="G523" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H523" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I523" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J523" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K523" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L523" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M523" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N523" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="524" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="110" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B524" s="111" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C524" s="111">
+        <v>6381121310</v>
+      </c>
+      <c r="D524" s="111" t="s">
+        <v>129</v>
+      </c>
+      <c r="E524" s="111" t="s">
+        <v>1497</v>
+      </c>
+      <c r="F524" s="112">
+        <v>45967</v>
+      </c>
+      <c r="G524" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H524" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I524" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J524" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K524" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L524" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M524" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N524" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="525" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="113" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B525" s="114" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C525" s="114">
+        <v>9361398904</v>
+      </c>
+      <c r="D525" s="114" t="s">
+        <v>110</v>
+      </c>
+      <c r="E525" s="114" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F525" s="115">
+        <v>45945</v>
+      </c>
+      <c r="G525" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H525" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I525" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J525" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K525" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L525" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M525" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N525" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="526" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="110" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B526" s="111" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C526" s="111">
+        <v>8838618512</v>
+      </c>
+      <c r="D526" s="111" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E526" s="111" t="s">
+        <v>321</v>
+      </c>
+      <c r="F526" s="112">
+        <v>45955</v>
+      </c>
+      <c r="G526" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H526" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I526" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J526" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K526" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L526" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M526" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N526" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="527" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="113" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B527" s="114" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C527" s="114">
+        <v>7539977912</v>
+      </c>
+      <c r="D527" s="114" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E527" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="F527" s="115">
+        <v>45968</v>
+      </c>
+      <c r="G527" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H527" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I527" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J527" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K527" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L527" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M527" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N527" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="528" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="110" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B528" s="111" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C528" s="111">
+        <v>7358531039</v>
+      </c>
+      <c r="D528" s="111" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E528" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F528" s="112">
+        <v>45938</v>
+      </c>
+      <c r="G528" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H528" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I528" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J528" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K528" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L528" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M528" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N528" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="529" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="113" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B529" s="114" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C529" s="114">
+        <v>8807645467</v>
+      </c>
+      <c r="D529" s="114" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E529" s="114" t="s">
+        <v>61</v>
+      </c>
+      <c r="F529" s="115">
+        <v>45958</v>
+      </c>
+      <c r="G529" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H529" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I529" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J529" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K529" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L529" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M529" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N529" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="530" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="110" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B530" s="111" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C530" s="111">
+        <v>9962866502</v>
+      </c>
+      <c r="D530" s="111" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E530" s="111" t="s">
+        <v>75</v>
+      </c>
+      <c r="F530" s="112">
+        <v>45968</v>
+      </c>
+      <c r="G530" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H530" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I530" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J530" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K530" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L530" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M530" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N530" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="531" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="113" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B531" s="114" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C531" s="114">
+        <v>8247537524</v>
+      </c>
+      <c r="D531" s="114" t="s">
+        <v>136</v>
+      </c>
+      <c r="E531" s="114" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F531" s="115">
+        <v>45955</v>
+      </c>
+      <c r="G531" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H531" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I531" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J531" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K531" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L531" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M531" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N531" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="532" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="110" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B532" s="111" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C532" s="111">
+        <v>8124215833</v>
+      </c>
+      <c r="D532" s="111" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E532" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F532" s="112">
+        <v>45968</v>
+      </c>
+      <c r="G532" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H532" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I532" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J532" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K532" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L532" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M532" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N532" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="533" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="113" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B533" s="114" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C533" s="114">
+        <v>9014191593</v>
+      </c>
+      <c r="D533" s="114" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E533" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F533" s="115">
+        <v>45891</v>
+      </c>
+      <c r="G533" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H533" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I533" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J533" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K533" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L533" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M533" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N533" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="534" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="110" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B534" s="111" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C534" s="111">
+        <v>9344983609</v>
+      </c>
+      <c r="D534" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="E534" s="111" t="s">
+        <v>61</v>
+      </c>
+      <c r="F534" s="112">
+        <v>45962</v>
+      </c>
+      <c r="G534" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H534" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I534" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J534" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K534" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L534" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M534" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N534" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="535" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="113" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B535" s="114" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C535" s="114">
+        <v>9363068424</v>
+      </c>
+      <c r="D535" s="114" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E535" s="114" t="s">
+        <v>699</v>
+      </c>
+      <c r="F535" s="115">
+        <v>45961</v>
+      </c>
+      <c r="G535" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H535" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I535" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J535" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K535" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L535" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M535" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N535" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="536" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="110" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B536" s="111" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C536" s="111">
+        <v>7010842323</v>
+      </c>
+      <c r="D536" s="111" t="s">
+        <v>647</v>
+      </c>
+      <c r="E536" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F536" s="112">
+        <v>45964</v>
+      </c>
+      <c r="G536" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H536" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I536" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J536" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K536" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L536" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M536" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N536" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="537" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="113" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B537" s="114" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C537" s="114">
+        <v>9791459019</v>
+      </c>
+      <c r="D537" s="114" t="s">
+        <v>474</v>
+      </c>
+      <c r="E537" s="114" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F537" s="115">
+        <v>45971</v>
+      </c>
+      <c r="G537" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H537" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I537" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J537" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K537" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L537" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M537" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N537" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="538" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="110" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B538" s="111" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C538" s="111">
+        <v>9345883503</v>
+      </c>
+      <c r="D538" s="111" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E538" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="F538" s="112">
+        <v>45947</v>
+      </c>
+      <c r="G538" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H538" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I538" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J538" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K538" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L538" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M538" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N538" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="539" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="113" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B539" s="114" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C539" s="114">
+        <v>9566112937</v>
+      </c>
+      <c r="D539" s="114" t="s">
+        <v>208</v>
+      </c>
+      <c r="E539" s="114" t="s">
+        <v>648</v>
+      </c>
+      <c r="F539" s="115">
+        <v>45924</v>
+      </c>
+      <c r="G539" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H539" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I539" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J539" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K539" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L539" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M539" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N539" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="540" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="110" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B540" s="111" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C540" s="111">
+        <v>9952043015</v>
+      </c>
+      <c r="D540" s="111" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E540" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="F540" s="112">
+        <v>45946</v>
+      </c>
+      <c r="G540" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H540" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I540" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J540" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K540" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L540" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M540" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N540" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="541" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="113" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B541" s="114" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C541" s="114">
+        <v>7548860648</v>
+      </c>
+      <c r="D541" s="114" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E541" s="124" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F541" s="115">
+        <v>45957</v>
+      </c>
+      <c r="G541" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H541" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I541" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J541" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K541" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L541" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M541" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N541" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="542" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="110" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B542" s="111" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C542" s="111">
+        <v>9398879951</v>
+      </c>
+      <c r="D542" s="111" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E542" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="F542" s="112">
+        <v>45960</v>
+      </c>
+      <c r="G542" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H542" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I542" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J542" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K542" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L542" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M542" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N542" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="543" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="113" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B543" s="114" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C543" s="114">
+        <v>8148724630</v>
+      </c>
+      <c r="D543" s="114" t="s">
+        <v>852</v>
+      </c>
+      <c r="E543" s="114" t="s">
+        <v>54</v>
+      </c>
+      <c r="F543" s="115">
+        <v>45971</v>
+      </c>
+      <c r="G543" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H543" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I543" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J543" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K543" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L543" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M543" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N543" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="544" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="110" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B544" s="111" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C544" s="111">
+        <v>7386159337</v>
+      </c>
+      <c r="D544" s="111" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E544" s="111" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F544" s="112">
+        <v>45948</v>
+      </c>
+      <c r="G544" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H544" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I544" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J544" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K544" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L544" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M544" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N544" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="545" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="113" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B545" s="114" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C545" s="114">
+        <v>8637435906</v>
+      </c>
+      <c r="D545" s="114" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E545" s="114" t="s">
+        <v>37</v>
+      </c>
+      <c r="F545" s="115">
+        <v>45964</v>
+      </c>
+      <c r="G545" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H545" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I545" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J545" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K545" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L545" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M545" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N545" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="546" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="110" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B546" s="111" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C546" s="111">
+        <v>9123522573</v>
+      </c>
+      <c r="D546" s="111" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E546" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="F546" s="112">
+        <v>45962</v>
+      </c>
+      <c r="G546" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H546" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I546" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J546" s="111" t="s">
+        <v>953</v>
+      </c>
+      <c r="K546" s="111" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L546" s="111" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M546" s="111" t="s">
+        <v>24</v>
+      </c>
+      <c r="N546" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="547" spans="1:14" ht="14.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="113" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B547" s="114" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C547" s="114">
+        <v>8092768846</v>
+      </c>
+      <c r="D547" s="114" t="s">
+        <v>1560</v>
+      </c>
+      <c r="E547" s="114" t="s">
+        <v>68</v>
+      </c>
+      <c r="F547" s="115">
+        <v>45952</v>
+      </c>
+      <c r="G547" s="123" t="s">
+        <v>18</v>
+      </c>
+      <c r="H547" s="121" t="s">
+        <v>19</v>
+      </c>
+      <c r="I547" s="123" t="s">
+        <v>724</v>
+      </c>
+      <c r="J547" s="114" t="s">
+        <v>953</v>
+      </c>
+      <c r="K547" s="114" t="s">
+        <v>1445</v>
+      </c>
+      <c r="L547" s="114" t="s">
+        <v>1446</v>
+      </c>
+      <c r="M547" s="114" t="s">
+        <v>24</v>
+      </c>
+      <c r="N547" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -26887,7 +29146,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F506"/>
+  <dimension ref="A1:F551"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.42578125" style="55" customWidth="1"/>
@@ -35206,6 +37465,738 @@
         <v>1366</v>
       </c>
     </row>
+    <row r="508" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="509" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A509" s="107" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B509" s="108">
+        <v>70</v>
+      </c>
+      <c r="C509" s="116" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D509" s="116" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E509" s="120" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A510" s="110" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B510" s="111">
+        <v>90</v>
+      </c>
+      <c r="C510" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D510" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E510" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A511" s="113" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B511" s="114">
+        <v>70</v>
+      </c>
+      <c r="C511" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D511" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E511" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A512" s="110" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B512" s="111">
+        <v>100</v>
+      </c>
+      <c r="C512" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D512" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E512" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A513" s="113" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B513" s="114">
+        <v>90</v>
+      </c>
+      <c r="C513" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D513" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E513" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A514" s="110" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B514" s="111">
+        <v>99</v>
+      </c>
+      <c r="C514" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D514" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E514" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A515" s="113" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B515" s="114">
+        <v>80</v>
+      </c>
+      <c r="C515" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D515" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E515" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A516" s="110" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B516" s="111">
+        <v>85</v>
+      </c>
+      <c r="C516" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D516" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E516" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A517" s="113" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B517" s="114">
+        <v>95</v>
+      </c>
+      <c r="C517" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D517" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E517" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A518" s="110" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B518" s="111">
+        <v>90</v>
+      </c>
+      <c r="C518" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D518" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E518" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A519" s="113" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B519" s="114">
+        <v>90</v>
+      </c>
+      <c r="C519" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D519" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E519" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A520" s="110" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B520" s="111">
+        <v>95</v>
+      </c>
+      <c r="C520" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D520" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E520" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A521" s="113" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B521" s="114">
+        <v>100</v>
+      </c>
+      <c r="C521" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D521" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E521" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A522" s="110" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B522" s="111">
+        <v>95</v>
+      </c>
+      <c r="C522" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D522" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E522" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A523" s="113" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B523" s="114">
+        <v>99</v>
+      </c>
+      <c r="C523" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D523" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E523" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A524" s="110" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B524" s="111">
+        <v>80</v>
+      </c>
+      <c r="C524" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D524" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E524" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A525" s="113" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B525" s="114">
+        <v>95</v>
+      </c>
+      <c r="C525" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D525" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E525" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A526" s="110" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B526" s="111">
+        <v>99</v>
+      </c>
+      <c r="C526" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D526" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E526" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A527" s="113" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B527" s="114">
+        <v>90</v>
+      </c>
+      <c r="C527" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D527" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E527" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A528" s="110" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B528" s="111">
+        <v>90</v>
+      </c>
+      <c r="C528" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D528" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E528" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A529" s="113" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B529" s="114">
+        <v>80</v>
+      </c>
+      <c r="C529" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D529" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E529" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A530" s="110" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B530" s="111">
+        <v>90</v>
+      </c>
+      <c r="C530" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D530" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E530" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A531" s="113" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B531" s="114">
+        <v>95</v>
+      </c>
+      <c r="C531" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D531" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E531" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A532" s="110" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B532" s="111">
+        <v>90</v>
+      </c>
+      <c r="C532" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D532" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E532" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A533" s="113" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B533" s="114">
+        <v>85</v>
+      </c>
+      <c r="C533" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D533" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E533" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A534" s="110" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B534" s="111">
+        <v>85</v>
+      </c>
+      <c r="C534" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D534" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E534" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A535" s="113" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B535" s="114">
+        <v>80</v>
+      </c>
+      <c r="C535" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D535" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E535" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A536" s="110" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B536" s="111">
+        <v>75</v>
+      </c>
+      <c r="C536" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D536" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E536" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A537" s="113" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B537" s="114">
+        <v>80</v>
+      </c>
+      <c r="C537" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D537" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E537" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A538" s="110" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B538" s="111">
+        <v>90</v>
+      </c>
+      <c r="C538" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D538" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E538" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A539" s="113" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B539" s="114">
+        <v>75</v>
+      </c>
+      <c r="C539" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D539" s="118" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E539" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A540" s="110" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B540" s="111">
+        <v>80</v>
+      </c>
+      <c r="C540" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D540" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E540" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A541" s="113" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B541" s="114">
+        <v>85</v>
+      </c>
+      <c r="C541" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D541" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E541" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A542" s="110" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B542" s="111">
+        <v>88</v>
+      </c>
+      <c r="C542" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D542" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E542" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A543" s="113" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B543" s="114">
+        <v>95</v>
+      </c>
+      <c r="C543" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D543" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E543" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A544" s="110" t="s">
+        <v>1538</v>
+      </c>
+      <c r="B544" s="111">
+        <v>80</v>
+      </c>
+      <c r="C544" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D544" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E544" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A545" s="113" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B545" s="114">
+        <v>85</v>
+      </c>
+      <c r="C545" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D545" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E545" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A546" s="110" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B546" s="111">
+        <v>75</v>
+      </c>
+      <c r="C546" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D546" s="117" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E546" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A547" s="113" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B547" s="114">
+        <v>90</v>
+      </c>
+      <c r="C547" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D547" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E547" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A548" s="110" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B548" s="111">
+        <v>95</v>
+      </c>
+      <c r="C548" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D548" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E548" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A549" s="113" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B549" s="114">
+        <v>80</v>
+      </c>
+      <c r="C549" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D549" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E549" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A550" s="110" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B550" s="111">
+        <v>85</v>
+      </c>
+      <c r="C550" s="117" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D550" s="117" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E550" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A551" s="113" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B551" s="114">
+        <v>80</v>
+      </c>
+      <c r="C551" s="118" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D551" s="118" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E551" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A29" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
@@ -35217,7 +38208,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J506"/>
+  <dimension ref="A1:J550"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.5703125" style="2" customWidth="1"/>
@@ -50854,6 +53845,1383 @@
         <v>1366</v>
       </c>
     </row>
+    <row r="507" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="508" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="107" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B508" s="108" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C508" s="108" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D508" s="108">
+        <v>6</v>
+      </c>
+      <c r="E508" s="108">
+        <v>7</v>
+      </c>
+      <c r="F508" s="108">
+        <v>6</v>
+      </c>
+      <c r="G508" s="108">
+        <v>4</v>
+      </c>
+      <c r="H508" s="108">
+        <v>4</v>
+      </c>
+      <c r="I508" s="108">
+        <v>27</v>
+      </c>
+      <c r="J508" s="120" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="110" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B509" s="111" t="s">
+        <v>1449</v>
+      </c>
+      <c r="C509" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D509" s="111">
+        <v>8</v>
+      </c>
+      <c r="E509" s="111">
+        <v>8</v>
+      </c>
+      <c r="F509" s="111">
+        <v>7</v>
+      </c>
+      <c r="G509" s="111">
+        <v>4</v>
+      </c>
+      <c r="H509" s="111">
+        <v>4</v>
+      </c>
+      <c r="I509" s="111">
+        <v>31</v>
+      </c>
+      <c r="J509" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="113" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B510" s="114" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C510" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D510" s="114">
+        <v>6</v>
+      </c>
+      <c r="E510" s="114">
+        <v>5</v>
+      </c>
+      <c r="F510" s="114">
+        <v>6</v>
+      </c>
+      <c r="G510" s="114">
+        <v>4</v>
+      </c>
+      <c r="H510" s="114">
+        <v>4</v>
+      </c>
+      <c r="I510" s="114">
+        <v>25</v>
+      </c>
+      <c r="J510" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="110" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B511" s="111" t="s">
+        <v>1455</v>
+      </c>
+      <c r="C511" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D511" s="111">
+        <v>8</v>
+      </c>
+      <c r="E511" s="111">
+        <v>8</v>
+      </c>
+      <c r="F511" s="111">
+        <v>9</v>
+      </c>
+      <c r="G511" s="111">
+        <v>8</v>
+      </c>
+      <c r="H511" s="111">
+        <v>7</v>
+      </c>
+      <c r="I511" s="111">
+        <v>40</v>
+      </c>
+      <c r="J511" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="113" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B512" s="114" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C512" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D512" s="114">
+        <v>8</v>
+      </c>
+      <c r="E512" s="114">
+        <v>7</v>
+      </c>
+      <c r="F512" s="114">
+        <v>7</v>
+      </c>
+      <c r="G512" s="114">
+        <v>4</v>
+      </c>
+      <c r="H512" s="114">
+        <v>4</v>
+      </c>
+      <c r="I512" s="114">
+        <v>30</v>
+      </c>
+      <c r="J512" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="110" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B513" s="111" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C513" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D513" s="111">
+        <v>8</v>
+      </c>
+      <c r="E513" s="111">
+        <v>7</v>
+      </c>
+      <c r="F513" s="111">
+        <v>8</v>
+      </c>
+      <c r="G513" s="111">
+        <v>8</v>
+      </c>
+      <c r="H513" s="111">
+        <v>6</v>
+      </c>
+      <c r="I513" s="111">
+        <v>37</v>
+      </c>
+      <c r="J513" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="113" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B514" s="114" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C514" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D514" s="114">
+        <v>7</v>
+      </c>
+      <c r="E514" s="114">
+        <v>7</v>
+      </c>
+      <c r="F514" s="114">
+        <v>6</v>
+      </c>
+      <c r="G514" s="114">
+        <v>4</v>
+      </c>
+      <c r="H514" s="114">
+        <v>4</v>
+      </c>
+      <c r="I514" s="114">
+        <v>28</v>
+      </c>
+      <c r="J514" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="110" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B515" s="111" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C515" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D515" s="111">
+        <v>8</v>
+      </c>
+      <c r="E515" s="111">
+        <v>8</v>
+      </c>
+      <c r="F515" s="111">
+        <v>7</v>
+      </c>
+      <c r="G515" s="111">
+        <v>4</v>
+      </c>
+      <c r="H515" s="111">
+        <v>4</v>
+      </c>
+      <c r="I515" s="111">
+        <v>31</v>
+      </c>
+      <c r="J515" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="113" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B516" s="114" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C516" s="125" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D516" s="125">
+        <v>8</v>
+      </c>
+      <c r="E516" s="125">
+        <v>9</v>
+      </c>
+      <c r="F516" s="125">
+        <v>7</v>
+      </c>
+      <c r="G516" s="114">
+        <v>6</v>
+      </c>
+      <c r="H516" s="114">
+        <v>6</v>
+      </c>
+      <c r="I516" s="114">
+        <v>36</v>
+      </c>
+      <c r="J516" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="110" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B517" s="111" t="s">
+        <v>1473</v>
+      </c>
+      <c r="C517" s="111" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D517" s="111">
+        <v>7</v>
+      </c>
+      <c r="E517" s="111">
+        <v>8</v>
+      </c>
+      <c r="F517" s="111">
+        <v>7</v>
+      </c>
+      <c r="G517" s="111">
+        <v>4</v>
+      </c>
+      <c r="H517" s="111">
+        <v>4</v>
+      </c>
+      <c r="I517" s="111">
+        <v>30</v>
+      </c>
+      <c r="J517" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="113" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B518" s="114" t="s">
+        <v>1476</v>
+      </c>
+      <c r="C518" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D518" s="114">
+        <v>7</v>
+      </c>
+      <c r="E518" s="114">
+        <v>8</v>
+      </c>
+      <c r="F518" s="114">
+        <v>8</v>
+      </c>
+      <c r="G518" s="114">
+        <v>4</v>
+      </c>
+      <c r="H518" s="114">
+        <v>4</v>
+      </c>
+      <c r="I518" s="114">
+        <v>31</v>
+      </c>
+      <c r="J518" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="110" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B519" s="111" t="s">
+        <v>1478</v>
+      </c>
+      <c r="C519" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D519" s="111">
+        <v>8</v>
+      </c>
+      <c r="E519" s="111">
+        <v>8</v>
+      </c>
+      <c r="F519" s="111">
+        <v>8</v>
+      </c>
+      <c r="G519" s="111">
+        <v>4</v>
+      </c>
+      <c r="H519" s="111">
+        <v>4</v>
+      </c>
+      <c r="I519" s="111">
+        <v>32</v>
+      </c>
+      <c r="J519" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="113" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B520" s="114" t="s">
+        <v>1481</v>
+      </c>
+      <c r="C520" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D520" s="114">
+        <v>7</v>
+      </c>
+      <c r="E520" s="114">
+        <v>8</v>
+      </c>
+      <c r="F520" s="114">
+        <v>9</v>
+      </c>
+      <c r="G520" s="114">
+        <v>6</v>
+      </c>
+      <c r="H520" s="114">
+        <v>5</v>
+      </c>
+      <c r="I520" s="114">
+        <v>35</v>
+      </c>
+      <c r="J520" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="110" t="s">
+        <v>1482</v>
+      </c>
+      <c r="B521" s="111" t="s">
+        <v>1483</v>
+      </c>
+      <c r="C521" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D521" s="111">
+        <v>7</v>
+      </c>
+      <c r="E521" s="111">
+        <v>7</v>
+      </c>
+      <c r="F521" s="111">
+        <v>7</v>
+      </c>
+      <c r="G521" s="111">
+        <v>8</v>
+      </c>
+      <c r="H521" s="111">
+        <v>7</v>
+      </c>
+      <c r="I521" s="111">
+        <v>36</v>
+      </c>
+      <c r="J521" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="113" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B522" s="114" t="s">
+        <v>1485</v>
+      </c>
+      <c r="C522" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D522" s="114">
+        <v>8</v>
+      </c>
+      <c r="E522" s="114">
+        <v>8</v>
+      </c>
+      <c r="F522" s="114">
+        <v>8</v>
+      </c>
+      <c r="G522" s="114">
+        <v>7</v>
+      </c>
+      <c r="H522" s="114">
+        <v>7</v>
+      </c>
+      <c r="I522" s="114">
+        <v>38</v>
+      </c>
+      <c r="J522" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="110" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B523" s="111" t="s">
+        <v>1487</v>
+      </c>
+      <c r="C523" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D523" s="111">
+        <v>7</v>
+      </c>
+      <c r="E523" s="111">
+        <v>8</v>
+      </c>
+      <c r="F523" s="111">
+        <v>8</v>
+      </c>
+      <c r="G523" s="111">
+        <v>4</v>
+      </c>
+      <c r="H523" s="111">
+        <v>4</v>
+      </c>
+      <c r="I523" s="111">
+        <v>31</v>
+      </c>
+      <c r="J523" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="113" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B524" s="114" t="s">
+        <v>1489</v>
+      </c>
+      <c r="C524" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D524" s="114">
+        <v>8</v>
+      </c>
+      <c r="E524" s="114">
+        <v>7</v>
+      </c>
+      <c r="F524" s="114">
+        <v>7</v>
+      </c>
+      <c r="G524" s="114">
+        <v>7</v>
+      </c>
+      <c r="H524" s="114">
+        <v>7</v>
+      </c>
+      <c r="I524" s="114">
+        <v>36</v>
+      </c>
+      <c r="J524" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="110" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B525" s="111" t="s">
+        <v>1491</v>
+      </c>
+      <c r="C525" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D525" s="111">
+        <v>8</v>
+      </c>
+      <c r="E525" s="111">
+        <v>8</v>
+      </c>
+      <c r="F525" s="111">
+        <v>9</v>
+      </c>
+      <c r="G525" s="111">
+        <v>4</v>
+      </c>
+      <c r="H525" s="111">
+        <v>4</v>
+      </c>
+      <c r="I525" s="111">
+        <v>33</v>
+      </c>
+      <c r="J525" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="113" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B526" s="114" t="s">
+        <v>1494</v>
+      </c>
+      <c r="C526" s="125" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D526" s="125">
+        <v>8</v>
+      </c>
+      <c r="E526" s="125">
+        <v>7</v>
+      </c>
+      <c r="F526" s="125">
+        <v>6</v>
+      </c>
+      <c r="G526" s="114">
+        <v>7</v>
+      </c>
+      <c r="H526" s="114">
+        <v>6</v>
+      </c>
+      <c r="I526" s="114">
+        <v>34</v>
+      </c>
+      <c r="J526" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="110" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B527" s="111" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C527" s="111" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D527" s="111">
+        <v>7</v>
+      </c>
+      <c r="E527" s="111">
+        <v>7</v>
+      </c>
+      <c r="F527" s="111">
+        <v>6</v>
+      </c>
+      <c r="G527" s="111">
+        <v>6</v>
+      </c>
+      <c r="H527" s="111">
+        <v>6</v>
+      </c>
+      <c r="I527" s="111">
+        <v>32</v>
+      </c>
+      <c r="J527" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="113" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B528" s="114" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C528" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D528" s="114">
+        <v>7</v>
+      </c>
+      <c r="E528" s="114">
+        <v>7</v>
+      </c>
+      <c r="F528" s="114">
+        <v>6</v>
+      </c>
+      <c r="G528" s="114">
+        <v>4</v>
+      </c>
+      <c r="H528" s="114">
+        <v>4</v>
+      </c>
+      <c r="I528" s="114">
+        <v>28</v>
+      </c>
+      <c r="J528" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="110" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B529" s="111" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C529" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D529" s="111">
+        <v>8</v>
+      </c>
+      <c r="E529" s="111">
+        <v>8</v>
+      </c>
+      <c r="F529" s="111">
+        <v>7</v>
+      </c>
+      <c r="G529" s="111">
+        <v>4</v>
+      </c>
+      <c r="H529" s="111">
+        <v>4</v>
+      </c>
+      <c r="I529" s="111">
+        <v>31</v>
+      </c>
+      <c r="J529" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="113" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B530" s="114" t="s">
+        <v>1505</v>
+      </c>
+      <c r="C530" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D530" s="114">
+        <v>8</v>
+      </c>
+      <c r="E530" s="114">
+        <v>8</v>
+      </c>
+      <c r="F530" s="114">
+        <v>7</v>
+      </c>
+      <c r="G530" s="114">
+        <v>8</v>
+      </c>
+      <c r="H530" s="114">
+        <v>7</v>
+      </c>
+      <c r="I530" s="114">
+        <v>38</v>
+      </c>
+      <c r="J530" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="110" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B531" s="111" t="s">
+        <v>1507</v>
+      </c>
+      <c r="C531" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D531" s="111">
+        <v>7</v>
+      </c>
+      <c r="E531" s="111">
+        <v>7</v>
+      </c>
+      <c r="F531" s="111">
+        <v>5</v>
+      </c>
+      <c r="G531" s="111">
+        <v>4</v>
+      </c>
+      <c r="H531" s="111">
+        <v>4</v>
+      </c>
+      <c r="I531" s="111">
+        <v>27</v>
+      </c>
+      <c r="J531" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="113" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B532" s="114" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C532" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D532" s="114">
+        <v>7</v>
+      </c>
+      <c r="E532" s="114">
+        <v>5</v>
+      </c>
+      <c r="F532" s="114">
+        <v>6</v>
+      </c>
+      <c r="G532" s="114">
+        <v>4</v>
+      </c>
+      <c r="H532" s="114">
+        <v>4</v>
+      </c>
+      <c r="I532" s="114">
+        <v>26</v>
+      </c>
+      <c r="J532" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="110" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B533" s="111" t="s">
+        <v>1513</v>
+      </c>
+      <c r="C533" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D533" s="111">
+        <v>7</v>
+      </c>
+      <c r="E533" s="111">
+        <v>8</v>
+      </c>
+      <c r="F533" s="111">
+        <v>7</v>
+      </c>
+      <c r="G533" s="111">
+        <v>4</v>
+      </c>
+      <c r="H533" s="111">
+        <v>4</v>
+      </c>
+      <c r="I533" s="111">
+        <v>30</v>
+      </c>
+      <c r="J533" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="113" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B534" s="114" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C534" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D534" s="114">
+        <v>7</v>
+      </c>
+      <c r="E534" s="114">
+        <v>6</v>
+      </c>
+      <c r="F534" s="114">
+        <v>5</v>
+      </c>
+      <c r="G534" s="114">
+        <v>5</v>
+      </c>
+      <c r="H534" s="114">
+        <v>5</v>
+      </c>
+      <c r="I534" s="114">
+        <v>28</v>
+      </c>
+      <c r="J534" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="110" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B535" s="111" t="s">
+        <v>1518</v>
+      </c>
+      <c r="C535" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D535" s="111">
+        <v>6</v>
+      </c>
+      <c r="E535" s="111">
+        <v>6</v>
+      </c>
+      <c r="F535" s="111">
+        <v>5</v>
+      </c>
+      <c r="G535" s="111">
+        <v>8</v>
+      </c>
+      <c r="H535" s="111">
+        <v>8</v>
+      </c>
+      <c r="I535" s="111">
+        <v>33</v>
+      </c>
+      <c r="J535" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" ht="24.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="113" t="s">
+        <v>1520</v>
+      </c>
+      <c r="B536" s="114" t="s">
+        <v>1521</v>
+      </c>
+      <c r="C536" s="125" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D536" s="125">
+        <v>7</v>
+      </c>
+      <c r="E536" s="125">
+        <v>7</v>
+      </c>
+      <c r="F536" s="125">
+        <v>5</v>
+      </c>
+      <c r="G536" s="114">
+        <v>4</v>
+      </c>
+      <c r="H536" s="114">
+        <v>4</v>
+      </c>
+      <c r="I536" s="114">
+        <v>27</v>
+      </c>
+      <c r="J536" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="110" t="s">
+        <v>1523</v>
+      </c>
+      <c r="B537" s="111" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C537" s="111" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D537" s="111">
+        <v>8</v>
+      </c>
+      <c r="E537" s="111">
+        <v>8</v>
+      </c>
+      <c r="F537" s="111">
+        <v>8</v>
+      </c>
+      <c r="G537" s="111">
+        <v>7</v>
+      </c>
+      <c r="H537" s="111">
+        <v>6</v>
+      </c>
+      <c r="I537" s="111">
+        <v>37</v>
+      </c>
+      <c r="J537" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="113" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B538" s="114" t="s">
+        <v>1526</v>
+      </c>
+      <c r="C538" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D538" s="114">
+        <v>7</v>
+      </c>
+      <c r="E538" s="114">
+        <v>5</v>
+      </c>
+      <c r="F538" s="114">
+        <v>6</v>
+      </c>
+      <c r="G538" s="114">
+        <v>4</v>
+      </c>
+      <c r="H538" s="114">
+        <v>4</v>
+      </c>
+      <c r="I538" s="114">
+        <v>26</v>
+      </c>
+      <c r="J538" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="110" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B539" s="111" t="s">
+        <v>1529</v>
+      </c>
+      <c r="C539" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D539" s="111">
+        <v>7</v>
+      </c>
+      <c r="E539" s="111">
+        <v>6</v>
+      </c>
+      <c r="F539" s="111">
+        <v>7</v>
+      </c>
+      <c r="G539" s="111">
+        <v>6</v>
+      </c>
+      <c r="H539" s="111">
+        <v>6</v>
+      </c>
+      <c r="I539" s="111">
+        <v>32</v>
+      </c>
+      <c r="J539" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="113" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B540" s="114" t="s">
+        <v>1531</v>
+      </c>
+      <c r="C540" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D540" s="114">
+        <v>7</v>
+      </c>
+      <c r="E540" s="114">
+        <v>8</v>
+      </c>
+      <c r="F540" s="114">
+        <v>6</v>
+      </c>
+      <c r="G540" s="114">
+        <v>4</v>
+      </c>
+      <c r="H540" s="114">
+        <v>4</v>
+      </c>
+      <c r="I540" s="114">
+        <v>29</v>
+      </c>
+      <c r="J540" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="110" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B541" s="111" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C541" s="111" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D541" s="111">
+        <v>8</v>
+      </c>
+      <c r="E541" s="111">
+        <v>8</v>
+      </c>
+      <c r="F541" s="111">
+        <v>5</v>
+      </c>
+      <c r="G541" s="111">
+        <v>7</v>
+      </c>
+      <c r="H541" s="111">
+        <v>6</v>
+      </c>
+      <c r="I541" s="111">
+        <v>34</v>
+      </c>
+      <c r="J541" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="113" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B542" s="114" t="s">
+        <v>1536</v>
+      </c>
+      <c r="C542" s="114" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D542" s="114">
+        <v>8</v>
+      </c>
+      <c r="E542" s="114">
+        <v>8</v>
+      </c>
+      <c r="F542" s="114">
+        <v>8</v>
+      </c>
+      <c r="G542" s="114">
+        <v>4</v>
+      </c>
+      <c r="H542" s="114">
+        <v>4</v>
+      </c>
+      <c r="I542" s="114">
+        <v>32</v>
+      </c>
+      <c r="J542" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="110" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B543" s="111" t="s">
+        <v>1538</v>
+      </c>
+      <c r="C543" s="111" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D543" s="111">
+        <v>7</v>
+      </c>
+      <c r="E543" s="111">
+        <v>8</v>
+      </c>
+      <c r="F543" s="111">
+        <v>7</v>
+      </c>
+      <c r="G543" s="111">
+        <v>7</v>
+      </c>
+      <c r="H543" s="111">
+        <v>6</v>
+      </c>
+      <c r="I543" s="111">
+        <v>35</v>
+      </c>
+      <c r="J543" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="113" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B544" s="114" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C544" s="114" t="s">
+        <v>1259</v>
+      </c>
+      <c r="D544" s="114">
+        <v>7</v>
+      </c>
+      <c r="E544" s="114">
+        <v>5</v>
+      </c>
+      <c r="F544" s="114">
+        <v>6</v>
+      </c>
+      <c r="G544" s="114">
+        <v>4</v>
+      </c>
+      <c r="H544" s="114">
+        <v>4</v>
+      </c>
+      <c r="I544" s="114">
+        <v>26</v>
+      </c>
+      <c r="J544" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="110" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B545" s="111" t="s">
+        <v>1545</v>
+      </c>
+      <c r="C545" s="111" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D545" s="111">
+        <v>7</v>
+      </c>
+      <c r="E545" s="111">
+        <v>4</v>
+      </c>
+      <c r="F545" s="111">
+        <v>6</v>
+      </c>
+      <c r="G545" s="111">
+        <v>4</v>
+      </c>
+      <c r="H545" s="111">
+        <v>4</v>
+      </c>
+      <c r="I545" s="111">
+        <v>25</v>
+      </c>
+      <c r="J545" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="113" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B546" s="114" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C546" s="125" t="s">
+        <v>1257</v>
+      </c>
+      <c r="D546" s="125">
+        <v>8</v>
+      </c>
+      <c r="E546" s="125">
+        <v>7</v>
+      </c>
+      <c r="F546" s="125">
+        <v>8</v>
+      </c>
+      <c r="G546" s="114">
+        <v>4</v>
+      </c>
+      <c r="H546" s="114">
+        <v>4</v>
+      </c>
+      <c r="I546" s="114">
+        <v>31</v>
+      </c>
+      <c r="J546" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="110" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B547" s="111" t="s">
+        <v>1550</v>
+      </c>
+      <c r="C547" s="111" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D547" s="111">
+        <v>8</v>
+      </c>
+      <c r="E547" s="111">
+        <v>6</v>
+      </c>
+      <c r="F547" s="111">
+        <v>6</v>
+      </c>
+      <c r="G547" s="111">
+        <v>4</v>
+      </c>
+      <c r="H547" s="111">
+        <v>4</v>
+      </c>
+      <c r="I547" s="111">
+        <v>28</v>
+      </c>
+      <c r="J547" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="113" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B548" s="114" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C548" s="114" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D548" s="114">
+        <v>7</v>
+      </c>
+      <c r="E548" s="114">
+        <v>8</v>
+      </c>
+      <c r="F548" s="114">
+        <v>7</v>
+      </c>
+      <c r="G548" s="114">
+        <v>4</v>
+      </c>
+      <c r="H548" s="114">
+        <v>4</v>
+      </c>
+      <c r="I548" s="114">
+        <v>30</v>
+      </c>
+      <c r="J548" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A549" s="110" t="s">
+        <v>1555</v>
+      </c>
+      <c r="B549" s="111" t="s">
+        <v>1556</v>
+      </c>
+      <c r="C549" s="111" t="s">
+        <v>1256</v>
+      </c>
+      <c r="D549" s="111">
+        <v>7</v>
+      </c>
+      <c r="E549" s="111">
+        <v>8</v>
+      </c>
+      <c r="F549" s="111">
+        <v>8</v>
+      </c>
+      <c r="G549" s="111">
+        <v>4</v>
+      </c>
+      <c r="H549" s="111">
+        <v>4</v>
+      </c>
+      <c r="I549" s="111">
+        <v>31</v>
+      </c>
+      <c r="J549" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A550" s="113" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B550" s="114" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C550" s="114" t="s">
+        <v>1258</v>
+      </c>
+      <c r="D550" s="114">
+        <v>7</v>
+      </c>
+      <c r="E550" s="114">
+        <v>7</v>
+      </c>
+      <c r="F550" s="114">
+        <v>7</v>
+      </c>
+      <c r="G550" s="114">
+        <v>4</v>
+      </c>
+      <c r="H550" s="114">
+        <v>4</v>
+      </c>
+      <c r="I550" s="114">
+        <v>29</v>
+      </c>
+      <c r="J550" s="121" t="s">
+        <v>1447</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C352" r:id="rId1" tooltip="https://www.geeksforgeeks.org/data-science/market-basket-analysis-in-data-mining/" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
